--- a/manutenção/modelo planilha auxiliar indicadores.xlsx
+++ b/manutenção/modelo planilha auxiliar indicadores.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PLANILHA" sheetId="1" r:id="rId1"/>
-    <sheet name="LISTAS" sheetId="2" r:id="rId2"/>
-    <sheet name="ATA" sheetId="4" r:id="rId3"/>
+    <sheet name="ATA" sheetId="4" r:id="rId2"/>
+    <sheet name="LISTAS" sheetId="2" r:id="rId3"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="207">
   <si>
     <t>FILIAL</t>
   </si>
@@ -647,6 +647,9 @@
   </si>
   <si>
     <t>GERAL</t>
+  </si>
+  <si>
+    <t>QTD</t>
   </si>
 </sst>
 </file>
@@ -742,7 +745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -753,12 +756,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -810,6 +807,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1143,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
@@ -1195,7 +1204,7 @@
       <c r="D2" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="24">
         <v>45078</v>
       </c>
       <c r="F2">
@@ -1203,13 +1212,16 @@
       </c>
       <c r="G2">
         <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="24">
         <v>45078</v>
       </c>
       <c r="F3">
@@ -1217,19 +1229,25 @@
       </c>
       <c r="G3">
         <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="24">
         <v>45078</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -1237,7 +1255,7 @@
       <c r="D5" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="24">
         <v>45078</v>
       </c>
       <c r="F5">
@@ -1245,13 +1263,16 @@
       </c>
       <c r="G5">
         <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="24">
         <v>45078</v>
       </c>
       <c r="F6">
@@ -1259,13 +1280,16 @@
       </c>
       <c r="G6">
         <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="24">
         <v>45078</v>
       </c>
       <c r="F7">
@@ -1273,19 +1297,25 @@
       </c>
       <c r="G7">
         <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="24">
         <v>45078</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>1</v>
       </c>
     </row>
@@ -1293,13 +1323,16 @@
       <c r="D9" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <v>45078</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
     </row>
@@ -1307,13 +1340,16 @@
       <c r="D10" t="s">
         <v>155</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="24">
         <v>45078</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
         <v>1</v>
       </c>
     </row>
@@ -1321,13 +1357,16 @@
       <c r="D11" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="24">
         <v>45078</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>1</v>
       </c>
     </row>
@@ -1335,13 +1374,16 @@
       <c r="D12" t="s">
         <v>157</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="24">
         <v>45078</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>1</v>
       </c>
     </row>
@@ -1349,13 +1391,16 @@
       <c r="D13" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="24">
         <v>45078</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0</v>
       </c>
     </row>
@@ -1363,7 +1408,7 @@
       <c r="D14" t="s">
         <v>159</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="24">
         <v>45078</v>
       </c>
       <c r="F14">
@@ -1371,13 +1416,16 @@
       </c>
       <c r="G14">
         <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>160</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="24">
         <v>45078</v>
       </c>
       <c r="F15">
@@ -1385,13 +1433,16 @@
       </c>
       <c r="G15">
         <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="24">
         <v>45078</v>
       </c>
       <c r="F16">
@@ -1400,12 +1451,15 @@
       <c r="G16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>162</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="24">
         <v>45078</v>
       </c>
       <c r="F17">
@@ -1414,12 +1468,15 @@
       <c r="G17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>163</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="24">
         <v>45078</v>
       </c>
       <c r="F18">
@@ -1428,12 +1485,15 @@
       <c r="G18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>164</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="24">
         <v>45078</v>
       </c>
       <c r="F19">
@@ -1442,12 +1502,15 @@
       <c r="G19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="24">
         <v>45078</v>
       </c>
       <c r="F20">
@@ -1456,12 +1519,15 @@
       <c r="G20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>166</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="24">
         <v>45078</v>
       </c>
       <c r="F21">
@@ -1470,12 +1536,15 @@
       <c r="G21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>167</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="24">
         <v>45078</v>
       </c>
       <c r="F22">
@@ -1484,12 +1553,15 @@
       <c r="G22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D23" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="24">
         <v>45078</v>
       </c>
       <c r="F23">
@@ -1498,12 +1570,15 @@
       <c r="G23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="24">
         <v>45078</v>
       </c>
       <c r="F24">
@@ -1512,12 +1587,15 @@
       <c r="G24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="24">
         <v>45078</v>
       </c>
       <c r="F25">
@@ -1526,12 +1604,15 @@
       <c r="G25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
         <v>171</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="24">
         <v>45078</v>
       </c>
       <c r="F26">
@@ -1540,12 +1621,15 @@
       <c r="G26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
         <v>172</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="24">
         <v>45078</v>
       </c>
       <c r="F27">
@@ -1554,12 +1638,15 @@
       <c r="G27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D28" t="s">
         <v>173</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="24">
         <v>45078</v>
       </c>
       <c r="F28">
@@ -1568,12 +1655,15 @@
       <c r="G28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
         <v>174</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="24">
         <v>45078</v>
       </c>
       <c r="F29">
@@ -1582,12 +1672,15 @@
       <c r="G29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
         <v>175</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="24">
         <v>45078</v>
       </c>
       <c r="F30">
@@ -1596,12 +1689,15 @@
       <c r="G30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="24">
         <v>45078</v>
       </c>
       <c r="F31">
@@ -1610,12 +1706,15 @@
       <c r="G31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>177</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="24">
         <v>45078</v>
       </c>
       <c r="F32">
@@ -1624,12 +1723,15 @@
       <c r="G32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>178</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="24">
         <v>45078</v>
       </c>
       <c r="F33">
@@ -1638,12 +1740,15 @@
       <c r="G33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
         <v>179</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="24">
         <v>45078</v>
       </c>
       <c r="F34">
@@ -1652,12 +1757,15 @@
       <c r="G34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
         <v>180</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="24">
         <v>45078</v>
       </c>
       <c r="F35">
@@ -1666,12 +1774,15 @@
       <c r="G35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
         <v>181</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="24">
         <v>45078</v>
       </c>
       <c r="F36">
@@ -1680,12 +1791,15 @@
       <c r="G36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
         <v>182</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="24">
         <v>45078</v>
       </c>
       <c r="F37">
@@ -1694,12 +1808,15 @@
       <c r="G37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
         <v>183</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="24">
         <v>45078</v>
       </c>
       <c r="F38">
@@ -1708,12 +1825,15 @@
       <c r="G38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="24">
         <v>45078</v>
       </c>
       <c r="F39">
@@ -1722,12 +1842,15 @@
       <c r="G39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
         <v>185</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="24">
         <v>45078</v>
       </c>
       <c r="F40">
@@ -1736,12 +1859,15 @@
       <c r="G40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
         <v>186</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="24">
         <v>45078</v>
       </c>
       <c r="F41">
@@ -1750,12 +1876,15 @@
       <c r="G41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D42" t="s">
         <v>187</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="24">
         <v>45078</v>
       </c>
       <c r="F42">
@@ -1764,12 +1893,15 @@
       <c r="G42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="24">
         <v>45078</v>
       </c>
       <c r="F43">
@@ -1778,12 +1910,15 @@
       <c r="G43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
         <v>189</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="24">
         <v>45078</v>
       </c>
       <c r="F44">
@@ -1792,12 +1927,15 @@
       <c r="G44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
         <v>190</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="24">
         <v>45078</v>
       </c>
       <c r="F45">
@@ -1806,12 +1944,15 @@
       <c r="G45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
         <v>191</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="24">
         <v>45078</v>
       </c>
       <c r="F46">
@@ -1820,12 +1961,15 @@
       <c r="G46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
         <v>192</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="24">
         <v>45078</v>
       </c>
       <c r="F47">
@@ -1834,12 +1978,15 @@
       <c r="G47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D48" t="s">
         <v>193</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="24">
         <v>45078</v>
       </c>
       <c r="F48">
@@ -1848,12 +1995,15 @@
       <c r="G48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D49" t="s">
         <v>194</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="24">
         <v>45078</v>
       </c>
       <c r="F49">
@@ -1862,12 +2012,15 @@
       <c r="G49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
         <v>195</v>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="24">
         <v>45078</v>
       </c>
       <c r="F50">
@@ -1876,12 +2029,15 @@
       <c r="G50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D51" t="s">
         <v>196</v>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="24">
         <v>45078</v>
       </c>
       <c r="F51">
@@ -1890,12 +2046,15 @@
       <c r="G51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D52" t="s">
         <v>197</v>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="24">
         <v>45078</v>
       </c>
       <c r="F52">
@@ -1904,12 +2063,15 @@
       <c r="G52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
         <v>198</v>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="24">
         <v>45078</v>
       </c>
       <c r="F53">
@@ -1918,12 +2080,15 @@
       <c r="G53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
         <v>199</v>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="24">
         <v>45078</v>
       </c>
       <c r="F54">
@@ -1932,12 +2097,15 @@
       <c r="G54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D55" t="s">
         <v>200</v>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="24">
         <v>45078</v>
       </c>
       <c r="F55">
@@ -1946,12 +2114,15 @@
       <c r="G55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D56" t="s">
         <v>201</v>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="24">
         <v>45078</v>
       </c>
       <c r="F56">
@@ -1960,12 +2131,15 @@
       <c r="G56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D57" t="s">
         <v>202</v>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="24">
         <v>45078</v>
       </c>
       <c r="F57">
@@ -1974,12 +2148,15 @@
       <c r="G57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D58" t="s">
         <v>203</v>
       </c>
-      <c r="E58" s="26">
+      <c r="E58" s="24">
         <v>45078</v>
       </c>
       <c r="F58">
@@ -1988,12 +2165,15 @@
       <c r="G58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D59" t="s">
         <v>144</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="24">
         <v>45078</v>
       </c>
       <c r="F59">
@@ -2002,12 +2182,15 @@
       <c r="G59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D60" t="s">
         <v>145</v>
       </c>
-      <c r="E60" s="26">
+      <c r="E60" s="24">
         <v>45078</v>
       </c>
       <c r="F60">
@@ -2016,12 +2199,15 @@
       <c r="G60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D61" t="s">
         <v>146</v>
       </c>
-      <c r="E61" s="26">
+      <c r="E61" s="24">
         <v>45078</v>
       </c>
       <c r="F61">
@@ -2030,12 +2216,15 @@
       <c r="G61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D62" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="26">
+      <c r="E62" s="24">
         <v>45078</v>
       </c>
       <c r="F62">
@@ -2044,13 +2233,16 @@
       <c r="G62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D63" t="s">
-        <v>147</v>
-      </c>
-      <c r="E63" s="26">
-        <v>45079</v>
+        <v>47</v>
+      </c>
+      <c r="E63" s="24">
+        <v>45078</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -2058,13 +2250,16 @@
       <c r="G63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D64" t="s">
-        <v>148</v>
-      </c>
-      <c r="E64" s="26">
-        <v>45079</v>
+        <v>48</v>
+      </c>
+      <c r="E64" s="24">
+        <v>45078</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -2072,13 +2267,16 @@
       <c r="G64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D65" t="s">
-        <v>149</v>
-      </c>
-      <c r="E65" s="26">
-        <v>45079</v>
+        <v>49</v>
+      </c>
+      <c r="E65" s="24">
+        <v>45078</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -2086,13 +2284,16 @@
       <c r="G65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D66" t="s">
-        <v>150</v>
-      </c>
-      <c r="E66" s="26">
-        <v>45079</v>
+        <v>50</v>
+      </c>
+      <c r="E66" s="24">
+        <v>45078</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -2100,13 +2301,16 @@
       <c r="G66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D67" t="s">
-        <v>151</v>
-      </c>
-      <c r="E67" s="26">
-        <v>45079</v>
+        <v>51</v>
+      </c>
+      <c r="E67" s="24">
+        <v>45078</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -2114,13 +2318,16 @@
       <c r="G67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D68" t="s">
-        <v>152</v>
-      </c>
-      <c r="E68" s="26">
-        <v>45079</v>
+        <v>52</v>
+      </c>
+      <c r="E68" s="24">
+        <v>45078</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -2128,13 +2335,16 @@
       <c r="G68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D69" t="s">
-        <v>153</v>
-      </c>
-      <c r="E69" s="26">
-        <v>45079</v>
+        <v>53</v>
+      </c>
+      <c r="E69" s="24">
+        <v>45078</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -2142,13 +2352,16 @@
       <c r="G69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D70" t="s">
-        <v>154</v>
-      </c>
-      <c r="E70" s="26">
-        <v>45079</v>
+        <v>54</v>
+      </c>
+      <c r="E70" s="24">
+        <v>45078</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -2156,13 +2369,16 @@
       <c r="G70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D71" t="s">
-        <v>155</v>
-      </c>
-      <c r="E71" s="26">
-        <v>45079</v>
+        <v>55</v>
+      </c>
+      <c r="E71" s="24">
+        <v>45078</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -2170,13 +2386,16 @@
       <c r="G71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D72" t="s">
-        <v>156</v>
-      </c>
-      <c r="E72" s="26">
-        <v>45079</v>
+        <v>56</v>
+      </c>
+      <c r="E72" s="24">
+        <v>45078</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -2184,13 +2403,16 @@
       <c r="G72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D73" t="s">
-        <v>157</v>
-      </c>
-      <c r="E73" s="26">
-        <v>45079</v>
+        <v>57</v>
+      </c>
+      <c r="E73" s="24">
+        <v>45078</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -2198,13 +2420,16 @@
       <c r="G73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D74" t="s">
-        <v>158</v>
-      </c>
-      <c r="E74" s="26">
-        <v>45079</v>
+        <v>58</v>
+      </c>
+      <c r="E74" s="24">
+        <v>45078</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -2212,13 +2437,16 @@
       <c r="G74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D75" t="s">
-        <v>159</v>
-      </c>
-      <c r="E75" s="26">
-        <v>45079</v>
+        <v>59</v>
+      </c>
+      <c r="E75" s="24">
+        <v>45078</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2226,13 +2454,16 @@
       <c r="G75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D76" t="s">
-        <v>160</v>
-      </c>
-      <c r="E76" s="26">
-        <v>45079</v>
+        <v>60</v>
+      </c>
+      <c r="E76" s="24">
+        <v>45078</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -2240,13 +2471,16 @@
       <c r="G76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D77" t="s">
-        <v>161</v>
-      </c>
-      <c r="E77" s="26">
-        <v>45079</v>
+        <v>61</v>
+      </c>
+      <c r="E77" s="24">
+        <v>45078</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -2254,13 +2488,16 @@
       <c r="G77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D78" t="s">
-        <v>162</v>
-      </c>
-      <c r="E78" s="26">
-        <v>45079</v>
+        <v>62</v>
+      </c>
+      <c r="E78" s="24">
+        <v>45078</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -2268,13 +2505,16 @@
       <c r="G78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D79" t="s">
-        <v>163</v>
-      </c>
-      <c r="E79" s="26">
-        <v>45079</v>
+        <v>63</v>
+      </c>
+      <c r="E79" s="24">
+        <v>45078</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -2282,167 +2522,203 @@
       <c r="G79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D80" t="s">
-        <v>164</v>
-      </c>
-      <c r="E80" s="26">
-        <v>45079</v>
+        <v>64</v>
+      </c>
+      <c r="E80" s="24">
+        <v>45078</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D81" t="s">
-        <v>165</v>
-      </c>
-      <c r="E81" s="26">
-        <v>45079</v>
+        <v>65</v>
+      </c>
+      <c r="E81" s="24">
+        <v>45078</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D82" t="s">
-        <v>166</v>
-      </c>
-      <c r="E82" s="26">
-        <v>45079</v>
+        <v>66</v>
+      </c>
+      <c r="E82" s="24">
+        <v>45078</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D83" t="s">
-        <v>167</v>
-      </c>
-      <c r="E83" s="26">
-        <v>45079</v>
+        <v>67</v>
+      </c>
+      <c r="E83" s="24">
+        <v>45078</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D84" t="s">
-        <v>168</v>
-      </c>
-      <c r="E84" s="26">
-        <v>45079</v>
+        <v>68</v>
+      </c>
+      <c r="E84" s="24">
+        <v>45078</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D85" t="s">
-        <v>169</v>
-      </c>
-      <c r="E85" s="26">
-        <v>45079</v>
+        <v>69</v>
+      </c>
+      <c r="E85" s="24">
+        <v>45078</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D86" t="s">
-        <v>170</v>
-      </c>
-      <c r="E86" s="26">
-        <v>45079</v>
+        <v>70</v>
+      </c>
+      <c r="E86" s="24">
+        <v>45078</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D87" t="s">
-        <v>171</v>
-      </c>
-      <c r="E87" s="26">
-        <v>45079</v>
+        <v>71</v>
+      </c>
+      <c r="E87" s="24">
+        <v>45078</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D88" t="s">
-        <v>172</v>
-      </c>
-      <c r="E88" s="26">
-        <v>45079</v>
+        <v>72</v>
+      </c>
+      <c r="E88" s="24">
+        <v>45078</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D89" t="s">
-        <v>173</v>
-      </c>
-      <c r="E89" s="26">
-        <v>45079</v>
+        <v>73</v>
+      </c>
+      <c r="E89" s="24">
+        <v>45078</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D90" t="s">
-        <v>174</v>
-      </c>
-      <c r="E90" s="26">
-        <v>45079</v>
+        <v>74</v>
+      </c>
+      <c r="E90" s="24">
+        <v>45078</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D91" t="s">
-        <v>175</v>
-      </c>
-      <c r="E91" s="26">
-        <v>45079</v>
+        <v>75</v>
+      </c>
+      <c r="E91" s="24">
+        <v>45078</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -2450,13 +2726,16 @@
       <c r="G91">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D92" t="s">
-        <v>176</v>
-      </c>
-      <c r="E92" s="26">
-        <v>45079</v>
+        <v>76</v>
+      </c>
+      <c r="E92" s="24">
+        <v>45078</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -2464,13 +2743,16 @@
       <c r="G92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
-        <v>177</v>
-      </c>
-      <c r="E93" s="26">
-        <v>45079</v>
+        <v>77</v>
+      </c>
+      <c r="E93" s="24">
+        <v>45078</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -2478,13 +2760,16 @@
       <c r="G93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D94" t="s">
-        <v>178</v>
-      </c>
-      <c r="E94" s="26">
-        <v>45079</v>
+        <v>78</v>
+      </c>
+      <c r="E94" s="24">
+        <v>45078</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -2492,13 +2777,16 @@
       <c r="G94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D95" t="s">
-        <v>179</v>
-      </c>
-      <c r="E95" s="26">
-        <v>45079</v>
+        <v>79</v>
+      </c>
+      <c r="E95" s="24">
+        <v>45078</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -2506,13 +2794,16 @@
       <c r="G95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D96" t="s">
-        <v>180</v>
-      </c>
-      <c r="E96" s="26">
-        <v>45079</v>
+        <v>80</v>
+      </c>
+      <c r="E96" s="24">
+        <v>45078</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -2520,13 +2811,16 @@
       <c r="G96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D97" t="s">
-        <v>181</v>
-      </c>
-      <c r="E97" s="26">
-        <v>45079</v>
+        <v>81</v>
+      </c>
+      <c r="E97" s="24">
+        <v>45078</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -2534,13 +2828,16 @@
       <c r="G97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D98" t="s">
-        <v>182</v>
-      </c>
-      <c r="E98" s="26">
-        <v>45079</v>
+        <v>82</v>
+      </c>
+      <c r="E98" s="24">
+        <v>45078</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -2548,13 +2845,16 @@
       <c r="G98">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D99" t="s">
-        <v>183</v>
-      </c>
-      <c r="E99" s="26">
-        <v>45079</v>
+        <v>83</v>
+      </c>
+      <c r="E99" s="24">
+        <v>45078</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -2562,13 +2862,16 @@
       <c r="G99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D100" t="s">
-        <v>184</v>
-      </c>
-      <c r="E100" s="26">
-        <v>45079</v>
+        <v>84</v>
+      </c>
+      <c r="E100" s="24">
+        <v>45078</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -2576,13 +2879,16 @@
       <c r="G100">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D101" t="s">
-        <v>185</v>
-      </c>
-      <c r="E101" s="26">
-        <v>45079</v>
+        <v>85</v>
+      </c>
+      <c r="E101" s="24">
+        <v>45078</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -2590,13 +2896,16 @@
       <c r="G101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>186</v>
-      </c>
-      <c r="E102" s="26">
-        <v>45079</v>
+        <v>86</v>
+      </c>
+      <c r="E102" s="24">
+        <v>45078</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -2604,13 +2913,16 @@
       <c r="G102">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
-        <v>187</v>
-      </c>
-      <c r="E103" s="26">
-        <v>45079</v>
+        <v>87</v>
+      </c>
+      <c r="E103" s="24">
+        <v>45078</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -2618,13 +2930,16 @@
       <c r="G103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D104" t="s">
-        <v>188</v>
-      </c>
-      <c r="E104" s="26">
-        <v>45079</v>
+        <v>88</v>
+      </c>
+      <c r="E104" s="24">
+        <v>45078</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -2632,13 +2947,16 @@
       <c r="G104">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D105" t="s">
-        <v>189</v>
-      </c>
-      <c r="E105" s="26">
-        <v>45079</v>
+        <v>89</v>
+      </c>
+      <c r="E105" s="24">
+        <v>45078</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -2646,13 +2964,16 @@
       <c r="G105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D106" t="s">
-        <v>190</v>
-      </c>
-      <c r="E106" s="26">
-        <v>45079</v>
+        <v>90</v>
+      </c>
+      <c r="E106" s="24">
+        <v>45078</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -2660,13 +2981,16 @@
       <c r="G106">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D107" t="s">
-        <v>191</v>
-      </c>
-      <c r="E107" s="26">
-        <v>45079</v>
+        <v>91</v>
+      </c>
+      <c r="E107" s="24">
+        <v>45078</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -2674,13 +2998,16 @@
       <c r="G107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D108" t="s">
-        <v>192</v>
-      </c>
-      <c r="E108" s="26">
-        <v>45079</v>
+        <v>92</v>
+      </c>
+      <c r="E108" s="24">
+        <v>45078</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -2688,13 +3015,16 @@
       <c r="G108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D109" t="s">
-        <v>193</v>
-      </c>
-      <c r="E109" s="26">
-        <v>45079</v>
+        <v>93</v>
+      </c>
+      <c r="E109" s="24">
+        <v>45078</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -2702,13 +3032,16 @@
       <c r="G109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D110" t="s">
-        <v>194</v>
-      </c>
-      <c r="E110" s="26">
-        <v>45079</v>
+        <v>94</v>
+      </c>
+      <c r="E110" s="24">
+        <v>45078</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -2716,13 +3049,16 @@
       <c r="G110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D111" t="s">
-        <v>195</v>
-      </c>
-      <c r="E111" s="26">
-        <v>45079</v>
+        <v>95</v>
+      </c>
+      <c r="E111" s="24">
+        <v>45078</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -2730,13 +3066,16 @@
       <c r="G111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E112" s="26">
-        <v>45079</v>
+        <v>96</v>
+      </c>
+      <c r="E112" s="24">
+        <v>45078</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -2744,13 +3083,16 @@
       <c r="G112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D113" t="s">
-        <v>197</v>
-      </c>
-      <c r="E113" s="26">
-        <v>45079</v>
+        <v>97</v>
+      </c>
+      <c r="E113" s="24">
+        <v>45078</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -2758,13 +3100,16 @@
       <c r="G113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D114" t="s">
-        <v>198</v>
-      </c>
-      <c r="E114" s="26">
-        <v>45079</v>
+        <v>98</v>
+      </c>
+      <c r="E114" s="24">
+        <v>45078</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -2772,13 +3117,16 @@
       <c r="G114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D115" t="s">
-        <v>199</v>
-      </c>
-      <c r="E115" s="26">
-        <v>45079</v>
+        <v>99</v>
+      </c>
+      <c r="E115" s="24">
+        <v>45078</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -2786,13 +3134,16 @@
       <c r="G115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D116" t="s">
-        <v>200</v>
-      </c>
-      <c r="E116" s="26">
-        <v>45079</v>
+        <v>100</v>
+      </c>
+      <c r="E116" s="24">
+        <v>45078</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -2800,13 +3151,16 @@
       <c r="G116">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D117" t="s">
-        <v>201</v>
-      </c>
-      <c r="E117" s="26">
-        <v>45079</v>
+        <v>101</v>
+      </c>
+      <c r="E117" s="24">
+        <v>45078</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -2814,13 +3168,16 @@
       <c r="G117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D118" t="s">
-        <v>202</v>
-      </c>
-      <c r="E118" s="26">
-        <v>45079</v>
+        <v>102</v>
+      </c>
+      <c r="E118" s="24">
+        <v>45078</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -2828,13 +3185,16 @@
       <c r="G118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D119" t="s">
-        <v>203</v>
-      </c>
-      <c r="E119" s="26">
-        <v>45079</v>
+        <v>103</v>
+      </c>
+      <c r="E119" s="24">
+        <v>45078</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -2842,61 +3202,688 @@
       <c r="G119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D120" t="s">
-        <v>144</v>
-      </c>
-      <c r="E120" s="26">
-        <v>45079</v>
+        <v>104</v>
+      </c>
+      <c r="E120" s="24">
+        <v>45078</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D121" t="s">
-        <v>145</v>
-      </c>
-      <c r="E121" s="26">
-        <v>45079</v>
+        <v>105</v>
+      </c>
+      <c r="E121" s="24">
+        <v>45078</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D122" t="s">
-        <v>146</v>
-      </c>
-      <c r="E122" s="26">
-        <v>45079</v>
+        <v>106</v>
+      </c>
+      <c r="E122" s="24">
+        <v>45078</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D123" t="s">
-        <v>20</v>
-      </c>
-      <c r="E123" s="26">
-        <v>45079</v>
+        <v>107</v>
+      </c>
+      <c r="E123" s="24">
+        <v>45078</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123">
         <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>108</v>
+      </c>
+      <c r="E124" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>109</v>
+      </c>
+      <c r="E125" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>110</v>
+      </c>
+      <c r="E126" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>111</v>
+      </c>
+      <c r="E127" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>112</v>
+      </c>
+      <c r="E128" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>113</v>
+      </c>
+      <c r="E129" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>114</v>
+      </c>
+      <c r="E130" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>115</v>
+      </c>
+      <c r="E131" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>116</v>
+      </c>
+      <c r="E132" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>117</v>
+      </c>
+      <c r="E133" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>118</v>
+      </c>
+      <c r="E134" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>119</v>
+      </c>
+      <c r="E135" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>120</v>
+      </c>
+      <c r="E136" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>121</v>
+      </c>
+      <c r="E137" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>122</v>
+      </c>
+      <c r="E138" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>123</v>
+      </c>
+      <c r="E139" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>124</v>
+      </c>
+      <c r="E140" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>125</v>
+      </c>
+      <c r="E141" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>126</v>
+      </c>
+      <c r="E142" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>127</v>
+      </c>
+      <c r="E143" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>129</v>
+      </c>
+      <c r="E145" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>130</v>
+      </c>
+      <c r="E146" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>1</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>131</v>
+      </c>
+      <c r="E147" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>132</v>
+      </c>
+      <c r="E148" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>133</v>
+      </c>
+      <c r="E149" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>134</v>
+      </c>
+      <c r="E150" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>135</v>
+      </c>
+      <c r="E151" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>136</v>
+      </c>
+      <c r="E152" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>137</v>
+      </c>
+      <c r="E153" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>138</v>
+      </c>
+      <c r="E154" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>139</v>
+      </c>
+      <c r="E155" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>140</v>
+      </c>
+      <c r="E156" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>141</v>
+      </c>
+      <c r="E157" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>142</v>
+      </c>
+      <c r="E158" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>143</v>
+      </c>
+      <c r="E159" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2936,6 +3923,2475 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AC84"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" style="12" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" customWidth="1"/>
+    <col min="20" max="21" width="12.42578125" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="8">
+        <f>'[1]ATA REUNIÃO PCM 27.06'!P3</f>
+        <v>45104</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>45078</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F2" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A2,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1,Tabela1[[BEM MNT]:[BEM MNT]],LISTAS!$H$2:$H$10)+SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A2,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1,Tabela1[[BEM MNT]:[BEM MNT]],LISTAS!$I$2:$I$30)</f>
+        <v>2</v>
+      </c>
+      <c r="G2" s="13">
+        <f>F2/E2</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="25">
+        <v>45078</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="21" t="e">
+        <f>SUMIFS(Tabela1[DISPONIBILIDADE],Tabela1[[DATA]:[DATA]],VLOOKUP(J2,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1,LISTAS!F2:F120,"CM*")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O2" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(J2,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="P2" s="15">
+        <v>0.64</v>
+      </c>
+      <c r="Q2" s="25">
+        <v>45078</v>
+      </c>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q2,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V2" s="16">
+        <v>10</v>
+      </c>
+      <c r="Y2" s="24"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
+        <v>45079</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F3" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A3,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G3" s="17">
+        <f t="shared" ref="G3" si="0">F3/E3</f>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="25">
+        <v>45079</v>
+      </c>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="Q3" s="25">
+        <v>45079</v>
+      </c>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q3,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V3" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
+        <v>45080</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F4" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A4,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G4" s="17">
+        <f>F4/E4</f>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="25">
+        <v>45080</v>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="Q4" s="25">
+        <v>45080</v>
+      </c>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q4,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V4" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>45081</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F5" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A5,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G5" s="17">
+        <f t="shared" ref="G5:G32" si="1">F5/E5</f>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="25">
+        <v>45081</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="Q5" s="25">
+        <v>45081</v>
+      </c>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q5,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V5" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
+        <v>45082</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F6" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A6,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="25">
+        <v>45082</v>
+      </c>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="15">
+        <v>0.71</v>
+      </c>
+      <c r="Q6" s="25">
+        <v>45082</v>
+      </c>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q6,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V6" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
+        <v>45083</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F7" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A7,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G7" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="25">
+        <v>45083</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="15">
+        <v>0.74</v>
+      </c>
+      <c r="Q7" s="25">
+        <v>45083</v>
+      </c>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q7,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V7" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>45084</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F8" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A8,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G8" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="25">
+        <v>45084</v>
+      </c>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>45084</v>
+      </c>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q8,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V8" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
+        <v>45085</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F9" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A9,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G9" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="25">
+        <v>45085</v>
+      </c>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="15">
+        <v>0.73</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>45085</v>
+      </c>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q9,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V9" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
+        <v>45086</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F10" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A10,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G10" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10" s="25">
+        <v>45086</v>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="15">
+        <v>0.73</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>45086</v>
+      </c>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q10,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V10" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
+        <v>45087</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F11" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A11,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G11" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11" s="25">
+        <v>45087</v>
+      </c>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="15">
+        <v>0.73</v>
+      </c>
+      <c r="Q11" s="25">
+        <v>45087</v>
+      </c>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q11,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V11" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A12" s="25">
+        <v>45088</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F12" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A12,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12" s="25">
+        <v>45088</v>
+      </c>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="Q12" s="25">
+        <v>45088</v>
+      </c>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q12,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V12" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" s="25">
+        <v>45089</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F13" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A13,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13" s="25">
+        <v>45089</v>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="Q13" s="25">
+        <v>45089</v>
+      </c>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q13,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V13" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A14" s="25">
+        <v>45090</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F14" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A14,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G14" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14" s="25">
+        <v>45090</v>
+      </c>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="15">
+        <v>0.77</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>45090</v>
+      </c>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q14,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V14" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A15" s="25">
+        <v>45091</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F15" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A15,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G15" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="J15" s="25">
+        <v>45091</v>
+      </c>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="15">
+        <v>0.77</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>45091</v>
+      </c>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q15,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V15" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A16" s="25">
+        <v>45092</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F16" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A16,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G16" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" s="25">
+        <v>45092</v>
+      </c>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="Q16" s="25">
+        <v>45092</v>
+      </c>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q16,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V16" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="25">
+        <v>45093</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F17" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A17,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G17" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17" s="25">
+        <v>45093</v>
+      </c>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>45093</v>
+      </c>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q17,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V17" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="25">
+        <v>45094</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F18" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A18,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G18" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18" s="25">
+        <v>45094</v>
+      </c>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="Q18" s="25">
+        <v>45094</v>
+      </c>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q18,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V18" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="25">
+        <v>45095</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F19" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A19,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G19" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19" s="25">
+        <v>45095</v>
+      </c>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="Q19" s="25">
+        <v>45095</v>
+      </c>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q19,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V19" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>45096</v>
+      </c>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F20" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A20,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G20" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20" s="25">
+        <v>45096</v>
+      </c>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>45096</v>
+      </c>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q20,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V20" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>45097</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F21" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A21,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G21" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21" s="25">
+        <v>45097</v>
+      </c>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="15">
+        <v>0.77</v>
+      </c>
+      <c r="Q21" s="25">
+        <v>45097</v>
+      </c>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q21,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V21" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>45098</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F22" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A22,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G22" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22" s="25">
+        <v>45098</v>
+      </c>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>45098</v>
+      </c>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q22,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V22" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>45099</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F23" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A23,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G23" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23" s="25">
+        <v>45099</v>
+      </c>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="Q23" s="25">
+        <v>45099</v>
+      </c>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q23,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V23" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>45100</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F24" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A24,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G24" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="25">
+        <v>45100</v>
+      </c>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="15">
+        <v>0.81</v>
+      </c>
+      <c r="Q24" s="25">
+        <v>45100</v>
+      </c>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q24,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V24" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>45101</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F25" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A25,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G25" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="25">
+        <v>45101</v>
+      </c>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="Q25" s="25">
+        <v>45101</v>
+      </c>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q25,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V25" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>45102</v>
+      </c>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F26" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A26,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G26" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="25">
+        <v>45102</v>
+      </c>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="Q26" s="25">
+        <v>45102</v>
+      </c>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q26,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V26" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>45103</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F27" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A27,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G27" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="25">
+        <v>45103</v>
+      </c>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="Q27" s="25">
+        <v>45103</v>
+      </c>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q27,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V27" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>45104</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="11">
+        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
+        <v>21</v>
+      </c>
+      <c r="F28" s="12">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A28,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
+        <v>38</v>
+      </c>
+      <c r="G28" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="25">
+        <v>45104</v>
+      </c>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="Q28" s="25">
+        <v>45104</v>
+      </c>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q28,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V28" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>45105</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="11"/>
+      <c r="G29" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="25">
+        <v>45105</v>
+      </c>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="25">
+        <v>45105</v>
+      </c>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q29,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V29" s="16"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>45106</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="11"/>
+      <c r="G30" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="25">
+        <v>45106</v>
+      </c>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="25">
+        <v>45106</v>
+      </c>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q30,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V30" s="16"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>45107</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="11"/>
+      <c r="G31" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="25">
+        <v>45107</v>
+      </c>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="25">
+        <v>45107</v>
+      </c>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="21">
+        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q31,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
+        <v>26</v>
+      </c>
+      <c r="V31" s="16"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="11"/>
+      <c r="G32" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="21"/>
+      <c r="V32" s="16"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="19">
+        <f>SUM(E2:E32)</f>
+        <v>567</v>
+      </c>
+      <c r="F33" s="20">
+        <f>SUM(F2:F32)</f>
+        <v>990</v>
+      </c>
+      <c r="G33" s="17">
+        <f>F33/E33</f>
+        <v>1.746031746031746</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="15">
+        <f>SUM($P$2:$P$32)/COUNTA($P$2:$P$32)</f>
+        <v>0.78666666666666651</v>
+      </c>
+      <c r="Q33" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="16">
+        <f>SUM($V$2:$V$32)/COUNTA($V$2:$V$32)</f>
+        <v>6.0370370370370372</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" s="25"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="21"/>
+      <c r="O34" s="21"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="26"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="26"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" s="25"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" s="25"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" s="25"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21"/>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="21"/>
+      <c r="O40" s="21"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="21"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="25"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="21"/>
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" s="25"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" s="25"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="21"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" s="25"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="21"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="25"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="21"/>
+      <c r="O46" s="21"/>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="25"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="21"/>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="25"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="21"/>
+      <c r="O48" s="21"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="25"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="J49" s="25"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="21"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="25"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="25"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="21"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="25"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="21"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="25"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="25"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="25"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="21"/>
+      <c r="O56" s="21"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="25"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="21"/>
+      <c r="O57" s="21"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="25"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="21"/>
+      <c r="O58" s="21"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="25"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="21"/>
+      <c r="O59" s="21"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="25"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="21"/>
+      <c r="O60" s="21"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="25"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="21"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="25"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="26"/>
+      <c r="M62" s="26"/>
+      <c r="N62" s="21"/>
+      <c r="O62" s="21"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="25"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="21"/>
+      <c r="O63" s="21"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="21"/>
+      <c r="O64" s="21"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="25"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="J65" s="25"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="21"/>
+      <c r="O65" s="21"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="26"/>
+      <c r="M66" s="26"/>
+      <c r="N66" s="21"/>
+      <c r="O66" s="21"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="J67" s="25"/>
+      <c r="K67" s="26"/>
+      <c r="L67" s="26"/>
+      <c r="M67" s="26"/>
+      <c r="N67" s="21"/>
+      <c r="O67" s="21"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="J68" s="25"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="25"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="26"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="25"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="25"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="25"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="25"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
+      <c r="N75" s="21"/>
+      <c r="O75" s="21"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="25"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="21"/>
+      <c r="O76" s="21"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="25"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
+      <c r="N77" s="21"/>
+      <c r="O77" s="21"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="25"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="21"/>
+      <c r="O78" s="21"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="25"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
+      <c r="N79" s="21"/>
+      <c r="O79" s="21"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="21"/>
+      <c r="O80" s="21"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="25"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="21"/>
+      <c r="O81" s="21"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="25"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="26"/>
+      <c r="L82" s="26"/>
+      <c r="M82" s="26"/>
+      <c r="N82" s="21"/>
+      <c r="O82" s="21"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="25"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="26"/>
+      <c r="L83" s="26"/>
+      <c r="M83" s="26"/>
+      <c r="N83" s="21"/>
+      <c r="O83" s="21"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="25"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="26"/>
+      <c r="L84" s="26"/>
+      <c r="M84" s="26"/>
+      <c r="N84" s="21"/>
+      <c r="O84" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="202">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="Q10:T10"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="Q34:V34"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="J61:M61"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="J65:M65"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="J66:M66"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="J67:M67"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="J62:M62"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="J63:M63"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="J64:M64"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="J71:M71"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="J72:M72"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="J73:M73"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="J68:M68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="J69:M69"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="J70:M70"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="J77:M77"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="J79:M79"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="J74:M74"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="J76:M76"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="J84:M84"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="J81:M81"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="J82:M82"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4304,2168 +7760,4 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z84"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" style="14" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="10">
-        <f>'[1]ATA REUNIÃO PCM 27.06'!P3</f>
-        <v>45104</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
-        <v>45078</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F2" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A2,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>19</v>
-      </c>
-      <c r="G2" s="15">
-        <f>F2/E2</f>
-        <v>0.90476190476190477</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="12">
-        <v>45078</v>
-      </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="17">
-        <v>0.64</v>
-      </c>
-      <c r="O2" s="12">
-        <v>45078</v>
-      </c>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="18">
-        <v>10</v>
-      </c>
-      <c r="V2" s="26"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
-        <v>45079</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F3" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A3,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G3" s="19">
-        <f t="shared" ref="G3" si="0">F3/E3</f>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="12">
-        <v>45079</v>
-      </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="17">
-        <v>0.79</v>
-      </c>
-      <c r="O3" s="12">
-        <v>45079</v>
-      </c>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>45080</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F4" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A4,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G4" s="19">
-        <f>F4/E4</f>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="12">
-        <v>45080</v>
-      </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="17">
-        <v>0.79</v>
-      </c>
-      <c r="O4" s="12">
-        <v>45080</v>
-      </c>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
-        <v>45081</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F5" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A5,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G5" s="19">
-        <f t="shared" ref="G5:G32" si="1">F5/E5</f>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="12">
-        <v>45081</v>
-      </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="17">
-        <v>0.79</v>
-      </c>
-      <c r="O5" s="12">
-        <v>45081</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
-        <v>45082</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F6" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A6,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G6" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="12">
-        <v>45082</v>
-      </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="17">
-        <v>0.71</v>
-      </c>
-      <c r="O6" s="12">
-        <v>45082</v>
-      </c>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
-        <v>45083</v>
-      </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F7" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A7,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G7" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="12">
-        <v>45083</v>
-      </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="17">
-        <v>0.74</v>
-      </c>
-      <c r="O7" s="12">
-        <v>45083</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
-        <v>45084</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F8" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A8,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G8" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="12">
-        <v>45084</v>
-      </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="O8" s="12">
-        <v>45084</v>
-      </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
-        <v>45085</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F9" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A9,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G9" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="12">
-        <v>45085</v>
-      </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="17">
-        <v>0.73</v>
-      </c>
-      <c r="O9" s="12">
-        <v>45085</v>
-      </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
-        <v>45086</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F10" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A10,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G10" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10" s="12">
-        <v>45086</v>
-      </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="17">
-        <v>0.73</v>
-      </c>
-      <c r="O10" s="12">
-        <v>45086</v>
-      </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>45087</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F11" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A11,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G11" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11" s="12">
-        <v>45087</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="17">
-        <v>0.73</v>
-      </c>
-      <c r="O11" s="12">
-        <v>45087</v>
-      </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
-        <v>45088</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F12" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A12,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G12" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12" s="12">
-        <v>45088</v>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="17">
-        <v>0.86</v>
-      </c>
-      <c r="O12" s="12">
-        <v>45088</v>
-      </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
-        <v>45089</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F13" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A13,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G13" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13" s="12">
-        <v>45089</v>
-      </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="17">
-        <v>0.86</v>
-      </c>
-      <c r="O13" s="12">
-        <v>45089</v>
-      </c>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
-        <v>45090</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F14" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A14,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G14" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14" s="12">
-        <v>45090</v>
-      </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="17">
-        <v>0.77</v>
-      </c>
-      <c r="O14" s="12">
-        <v>45090</v>
-      </c>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>45091</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A15,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G15" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="J15" s="12">
-        <v>45091</v>
-      </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="17">
-        <v>0.77</v>
-      </c>
-      <c r="O15" s="12">
-        <v>45091</v>
-      </c>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>45092</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A16,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G16" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16" s="12">
-        <v>45092</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="17">
-        <v>0.82</v>
-      </c>
-      <c r="O16" s="12">
-        <v>45092</v>
-      </c>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>45093</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F17" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A17,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G17" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17" s="12">
-        <v>45093</v>
-      </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="17">
-        <v>0.82</v>
-      </c>
-      <c r="O17" s="12">
-        <v>45093</v>
-      </c>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
-        <v>45094</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F18" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A18,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G18" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18" s="12">
-        <v>45094</v>
-      </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="17">
-        <v>0.86</v>
-      </c>
-      <c r="O18" s="12">
-        <v>45094</v>
-      </c>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
-        <v>45095</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F19" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A19,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G19" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19" s="12">
-        <v>45095</v>
-      </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="17">
-        <v>0.86</v>
-      </c>
-      <c r="O19" s="12">
-        <v>45095</v>
-      </c>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
-        <v>45096</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F20" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A20,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G20" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20" s="12">
-        <v>45096</v>
-      </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="17">
-        <v>0.82</v>
-      </c>
-      <c r="O20" s="12">
-        <v>45096</v>
-      </c>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
-        <v>45097</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F21" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A21,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G21" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21" s="12">
-        <v>45097</v>
-      </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="17">
-        <v>0.77</v>
-      </c>
-      <c r="O21" s="12">
-        <v>45097</v>
-      </c>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>45098</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A22,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G22" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22" s="12">
-        <v>45098</v>
-      </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="17">
-        <v>0.82</v>
-      </c>
-      <c r="O22" s="12">
-        <v>45098</v>
-      </c>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>45099</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A23,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G23" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23" s="12">
-        <v>45099</v>
-      </c>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="17">
-        <v>0.78</v>
-      </c>
-      <c r="O23" s="12">
-        <v>45099</v>
-      </c>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
-        <v>45100</v>
-      </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F24" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A24,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G24" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="12">
-        <v>45100</v>
-      </c>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="17">
-        <v>0.81</v>
-      </c>
-      <c r="O24" s="12">
-        <v>45100</v>
-      </c>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>45101</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F25" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A25,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G25" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="12">
-        <v>45101</v>
-      </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="17">
-        <v>0.79</v>
-      </c>
-      <c r="O25" s="12">
-        <v>45101</v>
-      </c>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <v>45102</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F26" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A26,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G26" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="12">
-        <v>45102</v>
-      </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="17">
-        <v>0.79</v>
-      </c>
-      <c r="O26" s="12">
-        <v>45102</v>
-      </c>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
-        <v>45103</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A27,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G27" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="12">
-        <v>45103</v>
-      </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="O27" s="12">
-        <v>45103</v>
-      </c>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
-        <v>45104</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="13">
-        <f>COUNTA(LISTAS!$H$2:$H$10,LISTAS!$I$2:$I$30)</f>
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A28,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>15</v>
-      </c>
-      <c r="G28" s="19">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="12">
-        <v>45104</v>
-      </c>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="17">
-        <v>0.79</v>
-      </c>
-      <c r="O28" s="12">
-        <v>45104</v>
-      </c>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
-        <v>45105</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-      <c r="G29" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="12">
-        <v>45105</v>
-      </c>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="12">
-        <v>45105</v>
-      </c>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="18"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
-        <v>45106</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="13"/>
-      <c r="G30" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="12">
-        <v>45106</v>
-      </c>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="12">
-        <v>45106</v>
-      </c>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="18"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
-        <v>45107</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="13"/>
-      <c r="G31" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="12">
-        <v>45107</v>
-      </c>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="12">
-        <v>45107</v>
-      </c>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="18"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="13"/>
-      <c r="G32" s="19" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="18"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="21">
-        <f>SUM(E2:E32)</f>
-        <v>567</v>
-      </c>
-      <c r="F33" s="22">
-        <f>SUM(F2:F32)</f>
-        <v>409</v>
-      </c>
-      <c r="G33" s="19">
-        <f>F33/E33</f>
-        <v>0.72134038800705469</v>
-      </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="17">
-        <f>SUM($N$2:$N$32)/COUNTA($N$2:$N$32)</f>
-        <v>0.78666666666666651</v>
-      </c>
-      <c r="O33" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="18">
-        <f>SUM($S$2:$S$32)/COUNTA($S$2:$S$32)</f>
-        <v>6.0370370370370372</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
-      <c r="S34" s="23"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="23"/>
-      <c r="M44" s="23"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="23"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-      <c r="M48" s="23"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-      <c r="M54" s="23"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="23"/>
-      <c r="M56" s="23"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="23"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="23"/>
-      <c r="M59" s="23"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="J60" s="12"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="23"/>
-      <c r="M60" s="23"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="23"/>
-      <c r="M61" s="23"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="23"/>
-      <c r="L62" s="23"/>
-      <c r="M62" s="23"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="23"/>
-      <c r="L63" s="23"/>
-      <c r="M63" s="23"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="23"/>
-      <c r="L65" s="23"/>
-      <c r="M65" s="23"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="23"/>
-      <c r="L66" s="23"/>
-      <c r="M66" s="23"/>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="12"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="23"/>
-      <c r="L67" s="23"/>
-      <c r="M67" s="23"/>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="12"/>
-      <c r="B68" s="23"/>
-      <c r="C68" s="23"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="23"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="12"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="23"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="12"/>
-      <c r="B70" s="23"/>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="J70" s="12"/>
-      <c r="K70" s="23"/>
-      <c r="L70" s="23"/>
-      <c r="M70" s="23"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="12"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="23"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="12"/>
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
-      <c r="J72" s="12"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="23"/>
-      <c r="M72" s="23"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="12"/>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="23"/>
-      <c r="M73" s="23"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="12"/>
-      <c r="B74" s="23"/>
-      <c r="C74" s="23"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
-      <c r="J74" s="12"/>
-      <c r="K74" s="23"/>
-      <c r="L74" s="23"/>
-      <c r="M74" s="23"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="12"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
-      <c r="M75" s="23"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="12"/>
-      <c r="B76" s="23"/>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="23"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="12"/>
-      <c r="B77" s="23"/>
-      <c r="C77" s="23"/>
-      <c r="D77" s="23"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="23"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="23"/>
-      <c r="L77" s="23"/>
-      <c r="M77" s="23"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="12"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="J78" s="12"/>
-      <c r="K78" s="23"/>
-      <c r="L78" s="23"/>
-      <c r="M78" s="23"/>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="12"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="23"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="12"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="23"/>
-      <c r="M80" s="23"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="12"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="23"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="12"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="23"/>
-      <c r="L82" s="23"/>
-      <c r="M82" s="23"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="12"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="23"/>
-      <c r="L83" s="23"/>
-      <c r="M83" s="23"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="12"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="23"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="23"/>
-      <c r="L84" s="23"/>
-      <c r="M84" s="23"/>
-    </row>
-  </sheetData>
-  <mergeCells count="202">
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="J84:M84"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="J81:M81"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="J82:M82"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="J77:M77"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="J79:M79"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="J74:M74"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="J75:M75"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="J76:M76"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="J71:M71"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="J72:M72"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="J73:M73"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="J68:M68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="J69:M69"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="J65:M65"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="J66:M66"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="J67:M67"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="J62:M62"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="J63:M63"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="J64:M64"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="J61:M61"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="O34:S34"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="O2:R2"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/manutenção/modelo planilha auxiliar indicadores.xlsx
+++ b/manutenção/modelo planilha auxiliar indicadores.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715"/>
   </bookViews>
   <sheets>
     <sheet name="PLANILHA" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="207">
   <si>
     <t>FILIAL</t>
   </si>
@@ -810,14 +810,14 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1152,14 +1152,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J159"/>
+  <dimension ref="A1:J317"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.42578125" customWidth="1"/>
@@ -3884,6 +3884,1270 @@
       </c>
       <c r="H159">
         <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>147</v>
+      </c>
+      <c r="E160" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="161" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>148</v>
+      </c>
+      <c r="E161" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="162" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>149</v>
+      </c>
+      <c r="E162" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="163" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>150</v>
+      </c>
+      <c r="E163" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="164" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>151</v>
+      </c>
+      <c r="E164" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="165" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>152</v>
+      </c>
+      <c r="E165" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="166" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>153</v>
+      </c>
+      <c r="E166" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="167" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>154</v>
+      </c>
+      <c r="E167" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="168" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>155</v>
+      </c>
+      <c r="E168" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="169" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>156</v>
+      </c>
+      <c r="E169" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="170" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>157</v>
+      </c>
+      <c r="E170" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="171" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>158</v>
+      </c>
+      <c r="E171" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="172" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>159</v>
+      </c>
+      <c r="E172" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="173" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>160</v>
+      </c>
+      <c r="E173" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="174" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>161</v>
+      </c>
+      <c r="E174" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="175" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>162</v>
+      </c>
+      <c r="E175" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="176" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>163</v>
+      </c>
+      <c r="E176" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="177" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>164</v>
+      </c>
+      <c r="E177" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="178" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>165</v>
+      </c>
+      <c r="E178" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="179" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>166</v>
+      </c>
+      <c r="E179" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="180" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>167</v>
+      </c>
+      <c r="E180" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="181" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D181" t="s">
+        <v>168</v>
+      </c>
+      <c r="E181" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="182" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D182" t="s">
+        <v>169</v>
+      </c>
+      <c r="E182" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="183" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D183" t="s">
+        <v>170</v>
+      </c>
+      <c r="E183" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="184" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D184" t="s">
+        <v>171</v>
+      </c>
+      <c r="E184" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="185" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D185" t="s">
+        <v>172</v>
+      </c>
+      <c r="E185" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="186" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D186" t="s">
+        <v>173</v>
+      </c>
+      <c r="E186" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="187" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
+        <v>174</v>
+      </c>
+      <c r="E187" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="188" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D188" t="s">
+        <v>175</v>
+      </c>
+      <c r="E188" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="189" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D189" t="s">
+        <v>176</v>
+      </c>
+      <c r="E189" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="190" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D190" t="s">
+        <v>177</v>
+      </c>
+      <c r="E190" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="191" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
+        <v>178</v>
+      </c>
+      <c r="E191" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="192" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D192" t="s">
+        <v>179</v>
+      </c>
+      <c r="E192" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="193" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
+        <v>180</v>
+      </c>
+      <c r="E193" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="194" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D194" t="s">
+        <v>181</v>
+      </c>
+      <c r="E194" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="195" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D195" t="s">
+        <v>182</v>
+      </c>
+      <c r="E195" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="196" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D196" t="s">
+        <v>183</v>
+      </c>
+      <c r="E196" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="197" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D197" t="s">
+        <v>184</v>
+      </c>
+      <c r="E197" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="198" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D198" t="s">
+        <v>185</v>
+      </c>
+      <c r="E198" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="199" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D199" t="s">
+        <v>186</v>
+      </c>
+      <c r="E199" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="200" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D200" t="s">
+        <v>187</v>
+      </c>
+      <c r="E200" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="201" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D201" t="s">
+        <v>188</v>
+      </c>
+      <c r="E201" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="202" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D202" t="s">
+        <v>189</v>
+      </c>
+      <c r="E202" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="203" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D203" t="s">
+        <v>190</v>
+      </c>
+      <c r="E203" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="204" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D204" t="s">
+        <v>191</v>
+      </c>
+      <c r="E204" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="205" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D205" t="s">
+        <v>192</v>
+      </c>
+      <c r="E205" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="206" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D206" t="s">
+        <v>193</v>
+      </c>
+      <c r="E206" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="207" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D207" t="s">
+        <v>194</v>
+      </c>
+      <c r="E207" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="208" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D208" t="s">
+        <v>195</v>
+      </c>
+      <c r="E208" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="209" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D209" t="s">
+        <v>196</v>
+      </c>
+      <c r="E209" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="210" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D210" t="s">
+        <v>197</v>
+      </c>
+      <c r="E210" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D211" t="s">
+        <v>198</v>
+      </c>
+      <c r="E211" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D212" t="s">
+        <v>199</v>
+      </c>
+      <c r="E212" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D213" t="s">
+        <v>200</v>
+      </c>
+      <c r="E213" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D214" t="s">
+        <v>201</v>
+      </c>
+      <c r="E214" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D215" t="s">
+        <v>202</v>
+      </c>
+      <c r="E215" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D216" t="s">
+        <v>203</v>
+      </c>
+      <c r="E216" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D217" t="s">
+        <v>144</v>
+      </c>
+      <c r="E217" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D218" t="s">
+        <v>145</v>
+      </c>
+      <c r="E218" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D219" t="s">
+        <v>146</v>
+      </c>
+      <c r="E219" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D220" t="s">
+        <v>20</v>
+      </c>
+      <c r="E220" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D221" t="s">
+        <v>47</v>
+      </c>
+      <c r="E221" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D222" t="s">
+        <v>48</v>
+      </c>
+      <c r="E222" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D223" t="s">
+        <v>49</v>
+      </c>
+      <c r="E223" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D224" t="s">
+        <v>50</v>
+      </c>
+      <c r="E224" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="225" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D225" t="s">
+        <v>51</v>
+      </c>
+      <c r="E225" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="226" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D226" t="s">
+        <v>52</v>
+      </c>
+      <c r="E226" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="227" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D227" t="s">
+        <v>53</v>
+      </c>
+      <c r="E227" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="228" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D228" t="s">
+        <v>54</v>
+      </c>
+      <c r="E228" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="229" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D229" t="s">
+        <v>55</v>
+      </c>
+      <c r="E229" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="230" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D230" t="s">
+        <v>56</v>
+      </c>
+      <c r="E230" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="231" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D231" t="s">
+        <v>57</v>
+      </c>
+      <c r="E231" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="232" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D232" t="s">
+        <v>58</v>
+      </c>
+      <c r="E232" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="233" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D233" t="s">
+        <v>59</v>
+      </c>
+      <c r="E233" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="234" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D234" t="s">
+        <v>60</v>
+      </c>
+      <c r="E234" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="235" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D235" t="s">
+        <v>61</v>
+      </c>
+      <c r="E235" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="236" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D236" t="s">
+        <v>62</v>
+      </c>
+      <c r="E236" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="237" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D237" t="s">
+        <v>63</v>
+      </c>
+      <c r="E237" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="238" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D238" t="s">
+        <v>64</v>
+      </c>
+      <c r="E238" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="239" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D239" t="s">
+        <v>65</v>
+      </c>
+      <c r="E239" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="240" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D240" t="s">
+        <v>66</v>
+      </c>
+      <c r="E240" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="241" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D241" t="s">
+        <v>67</v>
+      </c>
+      <c r="E241" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="242" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D242" t="s">
+        <v>68</v>
+      </c>
+      <c r="E242" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="243" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="244" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D244" t="s">
+        <v>70</v>
+      </c>
+      <c r="E244" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="245" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D245" t="s">
+        <v>71</v>
+      </c>
+      <c r="E245" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="246" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D246" t="s">
+        <v>72</v>
+      </c>
+      <c r="E246" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="247" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D247" t="s">
+        <v>73</v>
+      </c>
+      <c r="E247" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="248" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D248" t="s">
+        <v>74</v>
+      </c>
+      <c r="E248" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="249" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D249" t="s">
+        <v>75</v>
+      </c>
+      <c r="E249" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="250" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D250" t="s">
+        <v>76</v>
+      </c>
+      <c r="E250" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="251" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D251" t="s">
+        <v>77</v>
+      </c>
+      <c r="E251" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="252" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D252" t="s">
+        <v>78</v>
+      </c>
+      <c r="E252" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="253" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D253" t="s">
+        <v>79</v>
+      </c>
+      <c r="E253" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="254" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D254" t="s">
+        <v>80</v>
+      </c>
+      <c r="E254" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="255" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D255" t="s">
+        <v>81</v>
+      </c>
+      <c r="E255" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="256" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D256" t="s">
+        <v>82</v>
+      </c>
+      <c r="E256" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D257" t="s">
+        <v>83</v>
+      </c>
+      <c r="E257" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D258" t="s">
+        <v>84</v>
+      </c>
+      <c r="E258" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D259" t="s">
+        <v>85</v>
+      </c>
+      <c r="E259" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="260" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D260" t="s">
+        <v>86</v>
+      </c>
+      <c r="E260" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="261" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D261" t="s">
+        <v>87</v>
+      </c>
+      <c r="E261" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="262" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D262" t="s">
+        <v>88</v>
+      </c>
+      <c r="E262" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="263" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D263" t="s">
+        <v>89</v>
+      </c>
+      <c r="E263" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="264" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D264" t="s">
+        <v>90</v>
+      </c>
+      <c r="E264" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="265" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D265" t="s">
+        <v>91</v>
+      </c>
+      <c r="E265" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="266" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D266" t="s">
+        <v>92</v>
+      </c>
+      <c r="E266" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="267" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D267" t="s">
+        <v>93</v>
+      </c>
+      <c r="E267" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="268" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D268" t="s">
+        <v>94</v>
+      </c>
+      <c r="E268" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="269" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D269" t="s">
+        <v>95</v>
+      </c>
+      <c r="E269" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="270" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D270" t="s">
+        <v>96</v>
+      </c>
+      <c r="E270" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="271" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D271" t="s">
+        <v>97</v>
+      </c>
+      <c r="E271" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="272" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D272" t="s">
+        <v>98</v>
+      </c>
+      <c r="E272" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="273" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D273" t="s">
+        <v>99</v>
+      </c>
+      <c r="E273" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="274" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D274" t="s">
+        <v>100</v>
+      </c>
+      <c r="E274" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="275" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D275" t="s">
+        <v>101</v>
+      </c>
+      <c r="E275" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="276" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D276" t="s">
+        <v>102</v>
+      </c>
+      <c r="E276" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="277" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D277" t="s">
+        <v>103</v>
+      </c>
+      <c r="E277" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="278" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D278" t="s">
+        <v>104</v>
+      </c>
+      <c r="E278" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="279" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D279" t="s">
+        <v>105</v>
+      </c>
+      <c r="E279" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="280" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D280" t="s">
+        <v>106</v>
+      </c>
+      <c r="E280" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="281" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D281" t="s">
+        <v>107</v>
+      </c>
+      <c r="E281" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="282" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D282" t="s">
+        <v>108</v>
+      </c>
+      <c r="E282" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="283" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D283" t="s">
+        <v>109</v>
+      </c>
+      <c r="E283" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="284" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D284" t="s">
+        <v>110</v>
+      </c>
+      <c r="E284" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="285" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D285" t="s">
+        <v>111</v>
+      </c>
+      <c r="E285" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="286" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D286" t="s">
+        <v>112</v>
+      </c>
+      <c r="E286" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="287" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D287" t="s">
+        <v>113</v>
+      </c>
+      <c r="E287" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="288" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D288" t="s">
+        <v>114</v>
+      </c>
+      <c r="E288" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="289" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D289" t="s">
+        <v>115</v>
+      </c>
+      <c r="E289" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="290" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D290" t="s">
+        <v>116</v>
+      </c>
+      <c r="E290" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="291" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D291" t="s">
+        <v>117</v>
+      </c>
+      <c r="E291" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="292" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D292" t="s">
+        <v>118</v>
+      </c>
+      <c r="E292" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="293" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D293" t="s">
+        <v>119</v>
+      </c>
+      <c r="E293" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="294" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D294" t="s">
+        <v>120</v>
+      </c>
+      <c r="E294" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="295" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D295" t="s">
+        <v>121</v>
+      </c>
+      <c r="E295" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="296" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D296" t="s">
+        <v>122</v>
+      </c>
+      <c r="E296" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="297" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D297" t="s">
+        <v>123</v>
+      </c>
+      <c r="E297" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="298" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D298" t="s">
+        <v>124</v>
+      </c>
+      <c r="E298" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="299" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D299" t="s">
+        <v>125</v>
+      </c>
+      <c r="E299" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="300" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D300" t="s">
+        <v>126</v>
+      </c>
+      <c r="E300" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="301" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D301" t="s">
+        <v>127</v>
+      </c>
+      <c r="E301" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="302" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D302" t="s">
+        <v>128</v>
+      </c>
+      <c r="E302" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="303" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D303" t="s">
+        <v>129</v>
+      </c>
+      <c r="E303" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="304" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D304" t="s">
+        <v>130</v>
+      </c>
+      <c r="E304" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="305" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D305" t="s">
+        <v>131</v>
+      </c>
+      <c r="E305" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="306" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D306" t="s">
+        <v>132</v>
+      </c>
+      <c r="E306" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="307" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D307" t="s">
+        <v>133</v>
+      </c>
+      <c r="E307" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="308" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D308" t="s">
+        <v>134</v>
+      </c>
+      <c r="E308" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="309" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D309" t="s">
+        <v>135</v>
+      </c>
+      <c r="E309" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="310" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D310" t="s">
+        <v>136</v>
+      </c>
+      <c r="E310" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="311" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D311" t="s">
+        <v>137</v>
+      </c>
+      <c r="E311" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="312" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D312" t="s">
+        <v>138</v>
+      </c>
+      <c r="E312" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="313" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D313" t="s">
+        <v>139</v>
+      </c>
+      <c r="E313" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="314" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D314" t="s">
+        <v>140</v>
+      </c>
+      <c r="E314" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="315" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D315" t="s">
+        <v>141</v>
+      </c>
+      <c r="E315" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="316" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D316" t="s">
+        <v>142</v>
+      </c>
+      <c r="E316" s="24">
+        <v>45079</v>
+      </c>
+    </row>
+    <row r="317" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D317" t="s">
+        <v>143</v>
+      </c>
+      <c r="E317" s="24">
+        <v>45079</v>
       </c>
     </row>
   </sheetData>
@@ -3940,12 +5204,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
@@ -3962,12 +5226,12 @@
         <f>'[1]ATA REUNIÃO PCM 27.06'!P3</f>
         <v>45104</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
       <c r="N1" s="5" t="s">
         <v>30</v>
       </c>
@@ -3977,12 +5241,12 @@
       <c r="P1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="Q1" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
       <c r="U1" s="6" t="s">
         <v>206</v>
       </c>
@@ -4067,11 +5331,11 @@
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A3,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3" si="0">F3/E3</f>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>38</v>
@@ -4098,7 +5362,7 @@
       <c r="T3" s="25"/>
       <c r="U3" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q3,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V3" s="16">
         <v>8</v>
@@ -4117,11 +5381,11 @@
       </c>
       <c r="F4" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A4,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G4" s="17">
         <f>F4/E4</f>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>39</v>
@@ -4148,7 +5412,7 @@
       <c r="T4" s="25"/>
       <c r="U4" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q4,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V4" s="16">
         <v>8</v>
@@ -4167,11 +5431,11 @@
       </c>
       <c r="F5" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A5,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" ref="G5:G32" si="1">F5/E5</f>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>40</v>
@@ -4198,7 +5462,7 @@
       <c r="T5" s="25"/>
       <c r="U5" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q5,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V5" s="16">
         <v>8</v>
@@ -4217,11 +5481,11 @@
       </c>
       <c r="F6" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A6,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>41</v>
@@ -4248,7 +5512,7 @@
       <c r="T6" s="25"/>
       <c r="U6" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q6,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V6" s="16">
         <v>8</v>
@@ -4267,11 +5531,11 @@
       </c>
       <c r="F7" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A7,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>42</v>
@@ -4298,7 +5562,7 @@
       <c r="T7" s="25"/>
       <c r="U7" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q7,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V7" s="16">
         <v>8</v>
@@ -4317,11 +5581,11 @@
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A8,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>43</v>
@@ -4348,7 +5612,7 @@
       <c r="T8" s="25"/>
       <c r="U8" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q8,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V8" s="16">
         <v>7</v>
@@ -4367,11 +5631,11 @@
       </c>
       <c r="F9" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A9,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>44</v>
@@ -4398,7 +5662,7 @@
       <c r="T9" s="25"/>
       <c r="U9" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q9,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V9" s="16">
         <v>5</v>
@@ -4417,11 +5681,11 @@
       </c>
       <c r="F10" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A10,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
@@ -4444,7 +5708,7 @@
       <c r="T10" s="25"/>
       <c r="U10" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q10,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V10" s="16">
         <v>5</v>
@@ -4463,11 +5727,11 @@
       </c>
       <c r="F11" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A11,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
@@ -4490,7 +5754,7 @@
       <c r="T11" s="25"/>
       <c r="U11" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q11,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V11" s="16">
         <v>5</v>
@@ -4509,11 +5773,11 @@
       </c>
       <c r="F12" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A12,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
@@ -4536,7 +5800,7 @@
       <c r="T12" s="25"/>
       <c r="U12" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q12,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V12" s="16">
         <v>5</v>
@@ -4555,11 +5819,11 @@
       </c>
       <c r="F13" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A13,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G13" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
@@ -4582,7 +5846,7 @@
       <c r="T13" s="25"/>
       <c r="U13" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q13,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V13" s="16">
         <v>5</v>
@@ -4601,11 +5865,11 @@
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A14,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G14" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
@@ -4628,7 +5892,7 @@
       <c r="T14" s="25"/>
       <c r="U14" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q14,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V14" s="16">
         <v>5</v>
@@ -4647,11 +5911,11 @@
       </c>
       <c r="F15" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A15,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G15" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="J15" s="25">
         <v>45091</v>
@@ -4672,7 +5936,7 @@
       <c r="T15" s="25"/>
       <c r="U15" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q15,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V15" s="16">
         <v>5</v>
@@ -4691,11 +5955,11 @@
       </c>
       <c r="F16" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A16,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G16" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
@@ -4718,7 +5982,7 @@
       <c r="T16" s="25"/>
       <c r="U16" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q16,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V16" s="16">
         <v>5</v>
@@ -4737,11 +6001,11 @@
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A17,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G17" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
@@ -4764,7 +6028,7 @@
       <c r="T17" s="25"/>
       <c r="U17" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q17,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V17" s="16">
         <v>5</v>
@@ -4783,11 +6047,11 @@
       </c>
       <c r="F18" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A18,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G18" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
@@ -4810,7 +6074,7 @@
       <c r="T18" s="25"/>
       <c r="U18" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q18,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V18" s="16">
         <v>5</v>
@@ -4829,11 +6093,11 @@
       </c>
       <c r="F19" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A19,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G19" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
@@ -4856,7 +6120,7 @@
       <c r="T19" s="25"/>
       <c r="U19" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q19,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V19" s="16">
         <v>5</v>
@@ -4875,11 +6139,11 @@
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A20,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G20" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
@@ -4902,7 +6166,7 @@
       <c r="T20" s="25"/>
       <c r="U20" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q20,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V20" s="16">
         <v>5</v>
@@ -4921,11 +6185,11 @@
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A21,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G21" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
@@ -4948,7 +6212,7 @@
       <c r="T21" s="25"/>
       <c r="U21" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q21,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V21" s="16">
         <v>5</v>
@@ -4967,11 +6231,11 @@
       </c>
       <c r="F22" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A22,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G22" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
@@ -4994,7 +6258,7 @@
       <c r="T22" s="25"/>
       <c r="U22" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q22,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V22" s="16">
         <v>5</v>
@@ -5013,11 +6277,11 @@
       </c>
       <c r="F23" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A23,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G23" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
@@ -5040,7 +6304,7 @@
       <c r="T23" s="25"/>
       <c r="U23" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q23,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V23" s="16">
         <v>6</v>
@@ -5059,11 +6323,11 @@
       </c>
       <c r="F24" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A24,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G24" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
@@ -5086,7 +6350,7 @@
       <c r="T24" s="25"/>
       <c r="U24" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q24,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V24" s="16">
         <v>6</v>
@@ -5105,11 +6369,11 @@
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A25,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G25" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -5132,7 +6396,7 @@
       <c r="T25" s="25"/>
       <c r="U25" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q25,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V25" s="16">
         <v>6</v>
@@ -5151,11 +6415,11 @@
       </c>
       <c r="F26" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A26,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G26" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
@@ -5178,7 +6442,7 @@
       <c r="T26" s="25"/>
       <c r="U26" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q26,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V26" s="16">
         <v>6</v>
@@ -5197,11 +6461,11 @@
       </c>
       <c r="F27" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A27,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G27" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -5224,7 +6488,7 @@
       <c r="T27" s="25"/>
       <c r="U27" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q27,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V27" s="16">
         <v>6</v>
@@ -5243,11 +6507,11 @@
       </c>
       <c r="F28" s="12">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(A28,Tabela1[[DATA]:[DATA]],1),Tabela1[[DISPONIBILIDADE]:[DISPONIBILIDADE]],1)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G28" s="17">
         <f t="shared" si="1"/>
-        <v>1.8095238095238095</v>
+        <v>0</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
@@ -5270,7 +6534,7 @@
       <c r="T28" s="25"/>
       <c r="U28" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q28,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V28" s="16">
         <v>6</v>
@@ -5307,7 +6571,7 @@
       <c r="T29" s="25"/>
       <c r="U29" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q29,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V29" s="16"/>
     </row>
@@ -5342,7 +6606,7 @@
       <c r="T30" s="25"/>
       <c r="U30" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q30,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V30" s="16"/>
     </row>
@@ -5377,7 +6641,7 @@
       <c r="T31" s="25"/>
       <c r="U31" s="21">
         <f>SUMIFS(Tabela1[DISPONÍVEL],Tabela1[[DATA]:[DATA]],VLOOKUP(Q31,Tabela1[[DATA]:[DATA]],1),Tabela1[[AGUARDANDO PEÇAS]:[AGUARDANDO PEÇAS]],1)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V31" s="16"/>
     </row>
@@ -5420,11 +6684,11 @@
       </c>
       <c r="F33" s="20">
         <f>SUM(F2:F32)</f>
-        <v>990</v>
+        <v>2</v>
       </c>
       <c r="G33" s="17">
         <f>F33/E33</f>
-        <v>1.746031746031746</v>
+        <v>3.5273368606701938E-3</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="17"/>
@@ -5454,734 +6718,924 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
       <c r="J34" s="25"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
       <c r="N34" s="21"/>
       <c r="O34" s="21"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="26"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
       <c r="J35" s="25"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
       <c r="N35" s="21"/>
       <c r="O35" s="21"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="25"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
       <c r="H36" s="22"/>
       <c r="I36" s="22"/>
       <c r="J36" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
       <c r="N36" s="21"/>
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="25"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
       <c r="H37" s="23"/>
       <c r="I37" s="23"/>
       <c r="J37" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
       <c r="N37" s="21"/>
       <c r="O37" s="21"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
       <c r="J38" s="25"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
       <c r="N38" s="21"/>
       <c r="O38" s="21"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
       <c r="J39" s="25"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-      <c r="M39" s="26"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
       <c r="N39" s="21"/>
       <c r="O39" s="21"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
       <c r="J40" s="25"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
       <c r="J41" s="25"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
       <c r="N41" s="21"/>
       <c r="O41" s="21"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="25"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
       <c r="J42" s="25"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
       <c r="N42" s="21"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="25"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
       <c r="J43" s="25"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="26"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
       <c r="N43" s="21"/>
       <c r="O43" s="21"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="25"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
       <c r="J44" s="25"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
       <c r="N44" s="21"/>
       <c r="O44" s="21"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="25"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
       <c r="J45" s="25"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
       <c r="N45" s="21"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="25"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
       <c r="J46" s="25"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
       <c r="N46" s="21"/>
       <c r="O46" s="21"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="25"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
       <c r="J47" s="25"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
       <c r="N47" s="21"/>
       <c r="O47" s="21"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="25"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
       <c r="J48" s="25"/>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-      <c r="M48" s="26"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
       <c r="N48" s="21"/>
       <c r="O48" s="21"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="25"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
       <c r="J49" s="25"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
       <c r="N49" s="21"/>
       <c r="O49" s="21"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
       <c r="J50" s="25"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-      <c r="M50" s="26"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
       <c r="N50" s="21"/>
       <c r="O50" s="21"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="25"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
       <c r="J51" s="25"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
       <c r="N51" s="21"/>
       <c r="O51" s="21"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="25"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
       <c r="J52" s="25"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-      <c r="M52" s="26"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
       <c r="N52" s="21"/>
       <c r="O52" s="21"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="25"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
       <c r="J53" s="25"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="26"/>
+      <c r="K53" s="28"/>
+      <c r="L53" s="28"/>
+      <c r="M53" s="28"/>
       <c r="N53" s="21"/>
       <c r="O53" s="21"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="25"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
       <c r="J54" s="25"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
-      <c r="M54" s="26"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
       <c r="N54" s="21"/>
       <c r="O54" s="21"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="25"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
       <c r="J55" s="25"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="26"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
       <c r="N55" s="21"/>
       <c r="O55" s="21"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="25"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
       <c r="J56" s="25"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
-      <c r="M56" s="26"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="28"/>
       <c r="N56" s="21"/>
       <c r="O56" s="21"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="25"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
       <c r="J57" s="25"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="26"/>
-      <c r="M57" s="26"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
       <c r="N57" s="21"/>
       <c r="O57" s="21"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="25"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
       <c r="J58" s="25"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
-      <c r="M58" s="26"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
       <c r="N58" s="21"/>
       <c r="O58" s="21"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="25"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
       <c r="J59" s="25"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="26"/>
-      <c r="M59" s="26"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
       <c r="N59" s="21"/>
       <c r="O59" s="21"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="25"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
       <c r="J60" s="25"/>
-      <c r="K60" s="26"/>
-      <c r="L60" s="26"/>
-      <c r="M60" s="26"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="28"/>
       <c r="N60" s="21"/>
       <c r="O60" s="21"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="25"/>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
       <c r="J61" s="25"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
       <c r="N61" s="21"/>
       <c r="O61" s="21"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="25"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
       <c r="J62" s="25"/>
-      <c r="K62" s="26"/>
-      <c r="L62" s="26"/>
-      <c r="M62" s="26"/>
+      <c r="K62" s="28"/>
+      <c r="L62" s="28"/>
+      <c r="M62" s="28"/>
       <c r="N62" s="21"/>
       <c r="O62" s="21"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="25"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
       <c r="J63" s="25"/>
-      <c r="K63" s="26"/>
-      <c r="L63" s="26"/>
-      <c r="M63" s="26"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="28"/>
       <c r="N63" s="21"/>
       <c r="O63" s="21"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="25"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
       <c r="J64" s="25"/>
-      <c r="K64" s="26"/>
-      <c r="L64" s="26"/>
-      <c r="M64" s="26"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
       <c r="N64" s="21"/>
       <c r="O64" s="21"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="25"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
       <c r="J65" s="25"/>
-      <c r="K65" s="26"/>
-      <c r="L65" s="26"/>
-      <c r="M65" s="26"/>
+      <c r="K65" s="28"/>
+      <c r="L65" s="28"/>
+      <c r="M65" s="28"/>
       <c r="N65" s="21"/>
       <c r="O65" s="21"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="25"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
       <c r="J66" s="25"/>
-      <c r="K66" s="26"/>
-      <c r="L66" s="26"/>
-      <c r="M66" s="26"/>
+      <c r="K66" s="28"/>
+      <c r="L66" s="28"/>
+      <c r="M66" s="28"/>
       <c r="N66" s="21"/>
       <c r="O66" s="21"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="25"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
       <c r="J67" s="25"/>
-      <c r="K67" s="26"/>
-      <c r="L67" s="26"/>
-      <c r="M67" s="26"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
       <c r="N67" s="21"/>
       <c r="O67" s="21"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="25"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
       <c r="J68" s="25"/>
-      <c r="K68" s="26"/>
-      <c r="L68" s="26"/>
-      <c r="M68" s="26"/>
+      <c r="K68" s="28"/>
+      <c r="L68" s="28"/>
+      <c r="M68" s="28"/>
       <c r="N68" s="21"/>
       <c r="O68" s="21"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="25"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
       <c r="J69" s="25"/>
-      <c r="K69" s="26"/>
-      <c r="L69" s="26"/>
-      <c r="M69" s="26"/>
+      <c r="K69" s="28"/>
+      <c r="L69" s="28"/>
+      <c r="M69" s="28"/>
       <c r="N69" s="21"/>
       <c r="O69" s="21"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="25"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
       <c r="J70" s="25"/>
-      <c r="K70" s="26"/>
-      <c r="L70" s="26"/>
-      <c r="M70" s="26"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
       <c r="N70" s="21"/>
       <c r="O70" s="21"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="25"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
       <c r="J71" s="25"/>
-      <c r="K71" s="26"/>
-      <c r="L71" s="26"/>
-      <c r="M71" s="26"/>
+      <c r="K71" s="28"/>
+      <c r="L71" s="28"/>
+      <c r="M71" s="28"/>
       <c r="N71" s="21"/>
       <c r="O71" s="21"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="25"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
+      <c r="B72" s="28"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
       <c r="J72" s="25"/>
-      <c r="K72" s="26"/>
-      <c r="L72" s="26"/>
-      <c r="M72" s="26"/>
+      <c r="K72" s="28"/>
+      <c r="L72" s="28"/>
+      <c r="M72" s="28"/>
       <c r="N72" s="21"/>
       <c r="O72" s="21"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="25"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
+      <c r="B73" s="28"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
       <c r="J73" s="25"/>
-      <c r="K73" s="26"/>
-      <c r="L73" s="26"/>
-      <c r="M73" s="26"/>
+      <c r="K73" s="28"/>
+      <c r="L73" s="28"/>
+      <c r="M73" s="28"/>
       <c r="N73" s="21"/>
       <c r="O73" s="21"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="25"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26"/>
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
       <c r="J74" s="25"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
-      <c r="M74" s="26"/>
+      <c r="K74" s="28"/>
+      <c r="L74" s="28"/>
+      <c r="M74" s="28"/>
       <c r="N74" s="21"/>
       <c r="O74" s="21"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="25"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
       <c r="J75" s="25"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="26"/>
-      <c r="M75" s="26"/>
+      <c r="K75" s="28"/>
+      <c r="L75" s="28"/>
+      <c r="M75" s="28"/>
       <c r="N75" s="21"/>
       <c r="O75" s="21"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="25"/>
-      <c r="B76" s="26"/>
-      <c r="C76" s="26"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="26"/>
-      <c r="F76" s="26"/>
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
       <c r="J76" s="25"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
-      <c r="M76" s="26"/>
+      <c r="K76" s="28"/>
+      <c r="L76" s="28"/>
+      <c r="M76" s="28"/>
       <c r="N76" s="21"/>
       <c r="O76" s="21"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="25"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
+      <c r="B77" s="28"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
       <c r="J77" s="25"/>
-      <c r="K77" s="26"/>
-      <c r="L77" s="26"/>
-      <c r="M77" s="26"/>
+      <c r="K77" s="28"/>
+      <c r="L77" s="28"/>
+      <c r="M77" s="28"/>
       <c r="N77" s="21"/>
       <c r="O77" s="21"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="25"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
       <c r="J78" s="25"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="26"/>
-      <c r="M78" s="26"/>
+      <c r="K78" s="28"/>
+      <c r="L78" s="28"/>
+      <c r="M78" s="28"/>
       <c r="N78" s="21"/>
       <c r="O78" s="21"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="25"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
+      <c r="B79" s="28"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
       <c r="J79" s="25"/>
-      <c r="K79" s="26"/>
-      <c r="L79" s="26"/>
-      <c r="M79" s="26"/>
+      <c r="K79" s="28"/>
+      <c r="L79" s="28"/>
+      <c r="M79" s="28"/>
       <c r="N79" s="21"/>
       <c r="O79" s="21"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="25"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
+      <c r="B80" s="28"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="28"/>
       <c r="J80" s="25"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
+      <c r="K80" s="28"/>
+      <c r="L80" s="28"/>
+      <c r="M80" s="28"/>
       <c r="N80" s="21"/>
       <c r="O80" s="21"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="25"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
-      <c r="F81" s="26"/>
+      <c r="B81" s="28"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
       <c r="J81" s="25"/>
-      <c r="K81" s="26"/>
-      <c r="L81" s="26"/>
-      <c r="M81" s="26"/>
+      <c r="K81" s="28"/>
+      <c r="L81" s="28"/>
+      <c r="M81" s="28"/>
       <c r="N81" s="21"/>
       <c r="O81" s="21"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="25"/>
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="26"/>
-      <c r="F82" s="26"/>
+      <c r="B82" s="28"/>
+      <c r="C82" s="28"/>
+      <c r="D82" s="28"/>
+      <c r="E82" s="28"/>
+      <c r="F82" s="28"/>
       <c r="J82" s="25"/>
-      <c r="K82" s="26"/>
-      <c r="L82" s="26"/>
-      <c r="M82" s="26"/>
+      <c r="K82" s="28"/>
+      <c r="L82" s="28"/>
+      <c r="M82" s="28"/>
       <c r="N82" s="21"/>
       <c r="O82" s="21"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="25"/>
-      <c r="B83" s="26"/>
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
+      <c r="B83" s="28"/>
+      <c r="C83" s="28"/>
+      <c r="D83" s="28"/>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
       <c r="J83" s="25"/>
-      <c r="K83" s="26"/>
-      <c r="L83" s="26"/>
-      <c r="M83" s="26"/>
+      <c r="K83" s="28"/>
+      <c r="L83" s="28"/>
+      <c r="M83" s="28"/>
       <c r="N83" s="21"/>
       <c r="O83" s="21"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="25"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26"/>
+      <c r="B84" s="28"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="28"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
       <c r="J84" s="25"/>
-      <c r="K84" s="26"/>
-      <c r="L84" s="26"/>
-      <c r="M84" s="26"/>
+      <c r="K84" s="28"/>
+      <c r="L84" s="28"/>
+      <c r="M84" s="28"/>
       <c r="N84" s="21"/>
       <c r="O84" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="202">
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="J84:M84"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="J81:M81"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="J82:M82"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="J77:M77"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="J79:M79"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="J74:M74"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="J76:M76"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="J71:M71"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="J72:M72"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="J73:M73"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="J68:M68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="J69:M69"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="J70:M70"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="J65:M65"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="J66:M66"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="J67:M67"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="J62:M62"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="J63:M63"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="J64:M64"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="J61:M61"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="Q34:V34"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="Q10:T10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="Q6:T6"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="Q3:T3"/>
@@ -6194,196 +7648,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="Q5:T5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="Q9:T9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="Q10:T10"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="Q17:T17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="Q23:T23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="Q24:T24"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="Q22:T22"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="Q25:T25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="Q26:T26"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="Q32:T32"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q29:T29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="Q30:T30"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="Q33:T33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="Q34:V34"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="J61:M61"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="J65:M65"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="J66:M66"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="J67:M67"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="J62:M62"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="J63:M63"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="J64:M64"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="J71:M71"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="J72:M72"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="J73:M73"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="J68:M68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="J69:M69"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="J77:M77"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="J79:M79"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="J74:M74"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="J75:M75"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="J76:M76"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="J84:M84"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="J81:M81"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="J82:M82"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/manutenção/modelo planilha auxiliar indicadores.xlsx
+++ b/manutenção/modelo planilha auxiliar indicadores.xlsx
@@ -9,15 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PLANILHA" sheetId="1" r:id="rId1"/>
-    <sheet name="ATA" sheetId="4" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="2" r:id="rId3"/>
+    <sheet name="PLANILHA (2)" sheetId="5" r:id="rId2"/>
+    <sheet name="ATA" sheetId="4" r:id="rId3"/>
+    <sheet name="LISTAS" sheetId="2" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="207">
   <si>
     <t>FILIAL</t>
   </si>
@@ -656,7 +657,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -684,8 +685,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,8 +738,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor theme="6" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -740,12 +762,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="6"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -810,21 +843,37 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -871,7 +920,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:J3001" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:J3001" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:J3001"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="FILIAL"/>
+    <tableColumn id="2" name="CENTRO DE CUSTO"/>
+    <tableColumn id="3" name="ATIVIDADE"/>
+    <tableColumn id="4" name="BEM MNT"/>
+    <tableColumn id="5" name="DATA"/>
+    <tableColumn id="6" name="DISPONIBILIDADE"/>
+    <tableColumn id="7" name="DISPONÍVEL"/>
+    <tableColumn id="8" name="AGUARDANDO PEÇAS"/>
+    <tableColumn id="9" name="SERVIÇO EXTERNO"/>
+    <tableColumn id="10" name="PENDÊNCIA"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela13" displayName="Tabela13" ref="A1:J3001" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:J3001"/>
   <tableColumns count="10">
     <tableColumn id="1" name="FILIAL"/>
@@ -5187,6 +5255,3946 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:FQ317"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
+    <col min="28" max="173" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="31">
+        <v>45078</v>
+      </c>
+      <c r="Q1" s="31">
+        <v>45079</v>
+      </c>
+      <c r="R1" s="31">
+        <v>45080</v>
+      </c>
+      <c r="S1" s="31">
+        <v>45081</v>
+      </c>
+      <c r="T1" s="31">
+        <v>45082</v>
+      </c>
+      <c r="U1" s="31">
+        <v>45083</v>
+      </c>
+      <c r="V1" s="31">
+        <v>45084</v>
+      </c>
+      <c r="W1" s="31">
+        <v>45085</v>
+      </c>
+      <c r="X1" s="31">
+        <v>45086</v>
+      </c>
+      <c r="Y1" s="31">
+        <v>45087</v>
+      </c>
+      <c r="Z1" s="31">
+        <v>45088</v>
+      </c>
+      <c r="AA1" s="31">
+        <v>45089</v>
+      </c>
+      <c r="AB1" s="31">
+        <v>45090</v>
+      </c>
+      <c r="AC1" s="31">
+        <v>45091</v>
+      </c>
+      <c r="AD1" s="31">
+        <v>45092</v>
+      </c>
+      <c r="AE1" s="31">
+        <v>45093</v>
+      </c>
+      <c r="AF1" s="31">
+        <v>45094</v>
+      </c>
+      <c r="AG1" s="31">
+        <v>45095</v>
+      </c>
+      <c r="AH1" s="31">
+        <v>45096</v>
+      </c>
+      <c r="AI1" s="31">
+        <v>45097</v>
+      </c>
+      <c r="AJ1" s="31">
+        <v>45098</v>
+      </c>
+      <c r="AK1" s="31">
+        <v>45099</v>
+      </c>
+      <c r="AL1" s="31">
+        <v>45100</v>
+      </c>
+      <c r="AM1" s="31">
+        <v>45101</v>
+      </c>
+      <c r="AN1" s="31">
+        <v>45102</v>
+      </c>
+      <c r="AO1" s="31">
+        <v>45103</v>
+      </c>
+      <c r="AP1" s="31">
+        <v>45104</v>
+      </c>
+      <c r="AQ1" s="31">
+        <v>45105</v>
+      </c>
+      <c r="AR1" s="31">
+        <v>45106</v>
+      </c>
+      <c r="AS1" s="31">
+        <v>45107</v>
+      </c>
+      <c r="AT1" s="31"/>
+      <c r="AU1" s="33"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="33"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="33"/>
+      <c r="AZ1" s="31"/>
+      <c r="BA1" s="33"/>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="33"/>
+      <c r="BD1" s="31"/>
+      <c r="BE1" s="33"/>
+      <c r="BF1" s="31"/>
+      <c r="BG1" s="33"/>
+      <c r="BH1" s="31"/>
+      <c r="BI1" s="33"/>
+      <c r="BJ1" s="31"/>
+      <c r="BK1" s="33"/>
+      <c r="BL1" s="31"/>
+      <c r="BM1" s="33"/>
+      <c r="BN1" s="31"/>
+      <c r="BO1" s="33"/>
+      <c r="BP1" s="31"/>
+      <c r="BQ1" s="33"/>
+      <c r="BR1" s="31"/>
+      <c r="BS1" s="33"/>
+      <c r="BT1" s="31"/>
+      <c r="BU1" s="33"/>
+      <c r="BV1" s="31"/>
+      <c r="BW1" s="33"/>
+      <c r="BX1" s="31"/>
+      <c r="BY1" s="33"/>
+      <c r="BZ1" s="31"/>
+      <c r="CA1" s="33"/>
+      <c r="CB1" s="31"/>
+      <c r="CC1" s="33"/>
+      <c r="CD1" s="31"/>
+      <c r="CE1" s="33"/>
+      <c r="CF1" s="31"/>
+      <c r="CG1" s="33"/>
+      <c r="CH1" s="31"/>
+      <c r="CI1" s="33"/>
+      <c r="CJ1" s="31"/>
+      <c r="CK1" s="33"/>
+      <c r="CL1" s="31"/>
+      <c r="CM1" s="33"/>
+      <c r="CN1" s="31"/>
+      <c r="CO1" s="33"/>
+      <c r="CP1" s="31"/>
+      <c r="CQ1" s="33"/>
+      <c r="CR1" s="31"/>
+      <c r="CS1" s="33"/>
+      <c r="CT1" s="31"/>
+      <c r="CU1" s="33"/>
+      <c r="CV1" s="31"/>
+      <c r="CW1" s="33"/>
+      <c r="CX1" s="31"/>
+      <c r="CY1" s="33"/>
+      <c r="CZ1" s="31"/>
+      <c r="DA1" s="33"/>
+      <c r="DB1" s="31"/>
+      <c r="DC1" s="33"/>
+      <c r="DD1" s="31"/>
+      <c r="DE1" s="33"/>
+      <c r="DF1" s="31"/>
+      <c r="DG1" s="33"/>
+      <c r="DH1" s="31"/>
+      <c r="DI1" s="33"/>
+      <c r="DJ1" s="31"/>
+      <c r="DK1" s="33"/>
+      <c r="DL1" s="31"/>
+      <c r="DM1" s="33"/>
+      <c r="DN1" s="31"/>
+      <c r="DO1" s="33"/>
+      <c r="DP1" s="31"/>
+      <c r="DQ1" s="33"/>
+      <c r="DR1" s="31"/>
+      <c r="DS1" s="33"/>
+      <c r="DT1" s="31"/>
+      <c r="DU1" s="33"/>
+      <c r="DV1" s="31"/>
+      <c r="DW1" s="33"/>
+      <c r="DX1" s="31"/>
+      <c r="DY1" s="33"/>
+      <c r="DZ1" s="31"/>
+      <c r="EA1" s="33"/>
+      <c r="EB1" s="31"/>
+      <c r="EC1" s="33"/>
+      <c r="ED1" s="31"/>
+      <c r="EE1" s="33"/>
+      <c r="EF1" s="31"/>
+      <c r="EG1" s="33"/>
+      <c r="EH1" s="31"/>
+      <c r="EI1" s="33"/>
+      <c r="EJ1" s="31"/>
+      <c r="EK1" s="33"/>
+      <c r="EL1" s="31"/>
+      <c r="EM1" s="33"/>
+      <c r="EN1" s="31"/>
+      <c r="EO1" s="33"/>
+      <c r="EP1" s="31"/>
+      <c r="EQ1" s="33"/>
+      <c r="ER1" s="31"/>
+      <c r="ES1" s="33"/>
+      <c r="ET1" s="31"/>
+      <c r="EU1" s="33"/>
+      <c r="EV1" s="31"/>
+      <c r="EW1" s="33"/>
+      <c r="EX1" s="31"/>
+      <c r="EY1" s="33"/>
+      <c r="EZ1" s="31"/>
+      <c r="FA1" s="33"/>
+      <c r="FB1" s="31"/>
+      <c r="FC1" s="33"/>
+      <c r="FD1" s="31"/>
+      <c r="FE1" s="33"/>
+      <c r="FF1" s="31"/>
+      <c r="FG1" s="33"/>
+      <c r="FH1" s="31"/>
+      <c r="FI1" s="33"/>
+      <c r="FJ1" s="31"/>
+      <c r="FK1" s="33"/>
+      <c r="FL1" s="31"/>
+      <c r="FM1" s="33"/>
+      <c r="FN1" s="31"/>
+      <c r="FO1" s="33"/>
+      <c r="FP1" s="31"/>
+      <c r="FQ1" s="33"/>
+    </row>
+    <row r="2" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="32" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="O11" s="32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="32" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="O14" s="30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:173" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>161</v>
+      </c>
+      <c r="E16" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="32" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="O19" s="32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="32" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="O22" s="30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="O23" s="32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="O24" s="30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="O25" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="O26" s="30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E27" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="O27" s="32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="O28" s="30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="O29" s="32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="O30" s="30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="O31" s="32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="O32" s="30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>178</v>
+      </c>
+      <c r="E33" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="O33" s="32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="O35" s="32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>181</v>
+      </c>
+      <c r="E36" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="O37" s="32" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="O39" s="32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="O40" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="O41" s="32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="O42" s="30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="O43" s="32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="O44" s="30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="O45" s="32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="O46" s="30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="47" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>192</v>
+      </c>
+      <c r="E47" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="O47" s="32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="O48" s="30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="O49" s="32" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>195</v>
+      </c>
+      <c r="E50" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="O50" s="30" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="O51" s="32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>197</v>
+      </c>
+      <c r="E52" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="O52" s="30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>198</v>
+      </c>
+      <c r="E53" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="O53" s="32" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>199</v>
+      </c>
+      <c r="E54" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="O54" s="30" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>200</v>
+      </c>
+      <c r="E55" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="O55" s="32" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>201</v>
+      </c>
+      <c r="E56" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="O56" s="30" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="57" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="O57" s="32" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="58" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>203</v>
+      </c>
+      <c r="E58" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="O58" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="59" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>144</v>
+      </c>
+      <c r="E59" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="O59" s="32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>145</v>
+      </c>
+      <c r="E60" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="O60" s="30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="O61" s="32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="O62" s="30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="O63" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="O64" s="30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>49</v>
+      </c>
+      <c r="E65" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="O65" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="O66" s="30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="O67" s="32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="O68" s="30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="69" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="O69" s="32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="O70" s="30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="71" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>55</v>
+      </c>
+      <c r="E71" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="O71" s="32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="O72" s="30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>57</v>
+      </c>
+      <c r="E73" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="O73" s="32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="O74" s="30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="O75" s="32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>60</v>
+      </c>
+      <c r="E76" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="O76" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>61</v>
+      </c>
+      <c r="E77" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="O77" s="32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="O78" s="30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>63</v>
+      </c>
+      <c r="E79" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="O79" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="O80" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>65</v>
+      </c>
+      <c r="E81" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="O81" s="32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>66</v>
+      </c>
+      <c r="E82" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="O82" s="30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>67</v>
+      </c>
+      <c r="E83" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="O83" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>68</v>
+      </c>
+      <c r="E84" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="O84" s="30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="O85" s="32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>70</v>
+      </c>
+      <c r="E86" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="O86" s="30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>71</v>
+      </c>
+      <c r="E87" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="O87" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>72</v>
+      </c>
+      <c r="E88" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="O88" s="30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>73</v>
+      </c>
+      <c r="E89" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="O89" s="32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="90" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="O90" s="30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>75</v>
+      </c>
+      <c r="E91" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="O91" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>76</v>
+      </c>
+      <c r="E92" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="O92" s="30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="93" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>77</v>
+      </c>
+      <c r="E93" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="O93" s="32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>78</v>
+      </c>
+      <c r="E94" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="O94" s="30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>79</v>
+      </c>
+      <c r="E95" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="O95" s="32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>80</v>
+      </c>
+      <c r="E96" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="O96" s="30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>81</v>
+      </c>
+      <c r="E97" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="O97" s="32" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>82</v>
+      </c>
+      <c r="E98" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="O98" s="30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>83</v>
+      </c>
+      <c r="E99" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="O99" s="32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>84</v>
+      </c>
+      <c r="E100" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="O100" s="30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="101" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>85</v>
+      </c>
+      <c r="E101" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="O101" s="32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="102" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>86</v>
+      </c>
+      <c r="E102" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="O102" s="30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>87</v>
+      </c>
+      <c r="E103" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="O103" s="32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="104" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>88</v>
+      </c>
+      <c r="E104" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="O104" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="105" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>89</v>
+      </c>
+      <c r="E105" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="O105" s="32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="106" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>90</v>
+      </c>
+      <c r="E106" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="O106" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="107" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>91</v>
+      </c>
+      <c r="E107" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="O107" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="108" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>92</v>
+      </c>
+      <c r="E108" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="O108" s="30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="109" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>93</v>
+      </c>
+      <c r="E109" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="O109" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="110" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>94</v>
+      </c>
+      <c r="E110" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="O110" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="111" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>95</v>
+      </c>
+      <c r="E111" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="O111" s="32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="112" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>96</v>
+      </c>
+      <c r="E112" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="O112" s="30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="113" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>97</v>
+      </c>
+      <c r="E113" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="O113" s="32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>98</v>
+      </c>
+      <c r="E114" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="O114" s="30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="115" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>99</v>
+      </c>
+      <c r="E115" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="O115" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="116" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>100</v>
+      </c>
+      <c r="E116" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="O116" s="30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>101</v>
+      </c>
+      <c r="E117" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="O117" s="32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="118" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>102</v>
+      </c>
+      <c r="E118" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="O118" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="119" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>103</v>
+      </c>
+      <c r="E119" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="O119" s="32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="120" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>104</v>
+      </c>
+      <c r="E120" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="O120" s="30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>105</v>
+      </c>
+      <c r="E121" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="O121" s="32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="122" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>106</v>
+      </c>
+      <c r="E122" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="O122" s="30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="123" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>107</v>
+      </c>
+      <c r="E123" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="O123" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="124" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>108</v>
+      </c>
+      <c r="E124" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="O124" s="30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="125" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>109</v>
+      </c>
+      <c r="E125" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="O125" s="32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="126" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>110</v>
+      </c>
+      <c r="E126" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="O126" s="30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="127" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>111</v>
+      </c>
+      <c r="E127" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="O127" s="32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="128" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>112</v>
+      </c>
+      <c r="E128" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="O128" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="129" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>113</v>
+      </c>
+      <c r="E129" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="O129" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="130" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>114</v>
+      </c>
+      <c r="E130" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="O130" s="30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="131" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>115</v>
+      </c>
+      <c r="E131" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="O131" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="132" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>116</v>
+      </c>
+      <c r="E132" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="O132" s="30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="133" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>117</v>
+      </c>
+      <c r="E133" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="O133" s="32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="134" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>118</v>
+      </c>
+      <c r="E134" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="O134" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="135" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>119</v>
+      </c>
+      <c r="E135" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="O135" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="136" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>120</v>
+      </c>
+      <c r="E136" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="O136" s="30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="137" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>121</v>
+      </c>
+      <c r="E137" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="O137" s="32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="138" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>122</v>
+      </c>
+      <c r="E138" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="O138" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="139" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>123</v>
+      </c>
+      <c r="E139" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="O139" s="32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="140" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>124</v>
+      </c>
+      <c r="E140" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="O140" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="141" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>125</v>
+      </c>
+      <c r="E141" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="O141" s="32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="142" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>126</v>
+      </c>
+      <c r="E142" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="O142" s="30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="143" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>127</v>
+      </c>
+      <c r="E143" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="O143" s="32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="144" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="O144" s="30" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="145" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>129</v>
+      </c>
+      <c r="E145" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="O145" s="32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="146" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>130</v>
+      </c>
+      <c r="E146" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>1</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="O146" s="30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="147" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>131</v>
+      </c>
+      <c r="E147" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="O147" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="148" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>132</v>
+      </c>
+      <c r="E148" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="O148" s="30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="149" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>133</v>
+      </c>
+      <c r="E149" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="O149" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="150" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>134</v>
+      </c>
+      <c r="E150" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="O150" s="30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="151" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>135</v>
+      </c>
+      <c r="E151" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="O151" s="32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="152" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>136</v>
+      </c>
+      <c r="E152" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="O152" s="30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="153" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>137</v>
+      </c>
+      <c r="E153" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="O153" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="154" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>138</v>
+      </c>
+      <c r="E154" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="O154" s="30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="155" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>139</v>
+      </c>
+      <c r="E155" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="O155" s="32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="156" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>140</v>
+      </c>
+      <c r="E156" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="O156" s="30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>141</v>
+      </c>
+      <c r="E157" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="O157" s="32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="158" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>142</v>
+      </c>
+      <c r="E158" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="O158" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="159" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>143</v>
+      </c>
+      <c r="E159" s="24">
+        <v>45078</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="O159" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="160" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="E160" s="24"/>
+    </row>
+    <row r="161" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E161" s="24"/>
+    </row>
+    <row r="162" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E162" s="24"/>
+    </row>
+    <row r="163" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E163" s="24"/>
+    </row>
+    <row r="164" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E164" s="24"/>
+    </row>
+    <row r="165" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E165" s="24"/>
+    </row>
+    <row r="166" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E166" s="24"/>
+    </row>
+    <row r="167" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E167" s="24"/>
+    </row>
+    <row r="168" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E168" s="24"/>
+    </row>
+    <row r="169" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E169" s="24"/>
+    </row>
+    <row r="170" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E170" s="24"/>
+    </row>
+    <row r="171" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E171" s="24"/>
+    </row>
+    <row r="172" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E172" s="24"/>
+    </row>
+    <row r="173" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E173" s="24"/>
+    </row>
+    <row r="174" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E174" s="24"/>
+    </row>
+    <row r="175" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E175" s="24"/>
+    </row>
+    <row r="176" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E176" s="24"/>
+    </row>
+    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E177" s="24"/>
+    </row>
+    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E178" s="24"/>
+    </row>
+    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E179" s="24"/>
+    </row>
+    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E180" s="24"/>
+    </row>
+    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E181" s="24"/>
+    </row>
+    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E182" s="24"/>
+    </row>
+    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E183" s="24"/>
+    </row>
+    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E184" s="24"/>
+    </row>
+    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E185" s="24"/>
+    </row>
+    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E186" s="24"/>
+    </row>
+    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E187" s="24"/>
+    </row>
+    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E188" s="24"/>
+    </row>
+    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E189" s="24"/>
+    </row>
+    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E190" s="24"/>
+    </row>
+    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E191" s="24"/>
+    </row>
+    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E192" s="24"/>
+    </row>
+    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E193" s="24"/>
+    </row>
+    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E194" s="24"/>
+    </row>
+    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E195" s="24"/>
+    </row>
+    <row r="196" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E196" s="24"/>
+    </row>
+    <row r="197" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E197" s="24"/>
+    </row>
+    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E198" s="24"/>
+    </row>
+    <row r="199" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E199" s="24"/>
+    </row>
+    <row r="200" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E200" s="24"/>
+    </row>
+    <row r="201" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E201" s="24"/>
+    </row>
+    <row r="202" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E202" s="24"/>
+    </row>
+    <row r="203" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E203" s="24"/>
+    </row>
+    <row r="204" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E204" s="24"/>
+    </row>
+    <row r="205" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E205" s="24"/>
+    </row>
+    <row r="206" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E206" s="24"/>
+    </row>
+    <row r="207" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E207" s="24"/>
+    </row>
+    <row r="208" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E208" s="24"/>
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E209" s="24"/>
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E210" s="24"/>
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E211" s="24"/>
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E212" s="24"/>
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E213" s="24"/>
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E214" s="24"/>
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E215" s="24"/>
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E216" s="24"/>
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E217" s="24"/>
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E218" s="24"/>
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E219" s="24"/>
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E220" s="24"/>
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E221" s="24"/>
+    </row>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E222" s="24"/>
+    </row>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E223" s="24"/>
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E224" s="24"/>
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E225" s="24"/>
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E226" s="24"/>
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E227" s="24"/>
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E228" s="24"/>
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E229" s="24"/>
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E230" s="24"/>
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E231" s="24"/>
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E232" s="24"/>
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E233" s="24"/>
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E234" s="24"/>
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E235" s="24"/>
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E236" s="24"/>
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E237" s="24"/>
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E238" s="24"/>
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E239" s="24"/>
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E240" s="24"/>
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E241" s="24"/>
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E242" s="24"/>
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E243" s="24"/>
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E244" s="24"/>
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E245" s="24"/>
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E246" s="24"/>
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E247" s="24"/>
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E248" s="24"/>
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E249" s="24"/>
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E250" s="24"/>
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E251" s="24"/>
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E252" s="24"/>
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E253" s="24"/>
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E254" s="24"/>
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E255" s="24"/>
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E256" s="24"/>
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E257" s="24"/>
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E258" s="24"/>
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E259" s="24"/>
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E260" s="24"/>
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E261" s="24"/>
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E262" s="24"/>
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E263" s="24"/>
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E264" s="24"/>
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E265" s="24"/>
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E266" s="24"/>
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E267" s="24"/>
+    </row>
+    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E268" s="24"/>
+    </row>
+    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E269" s="24"/>
+    </row>
+    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E270" s="24"/>
+    </row>
+    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E271" s="24"/>
+    </row>
+    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E272" s="24"/>
+    </row>
+    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E273" s="24"/>
+    </row>
+    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E274" s="24"/>
+    </row>
+    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E275" s="24"/>
+    </row>
+    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E276" s="24"/>
+    </row>
+    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E277" s="24"/>
+    </row>
+    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E278" s="24"/>
+    </row>
+    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E279" s="24"/>
+    </row>
+    <row r="280" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E280" s="24"/>
+    </row>
+    <row r="281" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E281" s="24"/>
+    </row>
+    <row r="282" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E282" s="24"/>
+    </row>
+    <row r="283" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E283" s="24"/>
+    </row>
+    <row r="284" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E284" s="24"/>
+    </row>
+    <row r="285" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E285" s="24"/>
+    </row>
+    <row r="286" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E286" s="24"/>
+    </row>
+    <row r="287" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E287" s="24"/>
+    </row>
+    <row r="288" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E288" s="24"/>
+    </row>
+    <row r="289" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E289" s="24"/>
+    </row>
+    <row r="290" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E290" s="24"/>
+    </row>
+    <row r="291" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E291" s="24"/>
+    </row>
+    <row r="292" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E292" s="24"/>
+    </row>
+    <row r="293" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E293" s="24"/>
+    </row>
+    <row r="294" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E294" s="24"/>
+    </row>
+    <row r="295" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E295" s="24"/>
+    </row>
+    <row r="296" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E296" s="24"/>
+    </row>
+    <row r="297" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E297" s="24"/>
+    </row>
+    <row r="298" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E298" s="24"/>
+    </row>
+    <row r="299" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E299" s="24"/>
+    </row>
+    <row r="300" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E300" s="24"/>
+    </row>
+    <row r="301" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E301" s="24"/>
+    </row>
+    <row r="302" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E302" s="24"/>
+    </row>
+    <row r="303" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E303" s="24"/>
+    </row>
+    <row r="304" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E304" s="24"/>
+    </row>
+    <row r="305" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E305" s="24"/>
+    </row>
+    <row r="306" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E306" s="24"/>
+    </row>
+    <row r="307" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E307" s="24"/>
+    </row>
+    <row r="308" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E308" s="24"/>
+    </row>
+    <row r="309" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E309" s="24"/>
+    </row>
+    <row r="310" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E310" s="24"/>
+    </row>
+    <row r="311" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E311" s="24"/>
+    </row>
+    <row r="312" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E312" s="24"/>
+    </row>
+    <row r="313" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E313" s="24"/>
+    </row>
+    <row r="314" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E314" s="24"/>
+    </row>
+    <row r="315" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E315" s="24"/>
+    </row>
+    <row r="316" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E316" s="24"/>
+    </row>
+    <row r="317" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E317" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>LISTAS!$E$2:$E$160</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D3001 O2:O159</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>LISTAS!$A$2:$A$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J3001</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>LISTAS!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:I3001</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AC84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5204,12 +9212,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
       <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
@@ -5226,12 +9234,12 @@
         <f>'[1]ATA REUNIÃO PCM 27.06'!P3</f>
         <v>45104</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
       <c r="N1" s="5" t="s">
         <v>30</v>
       </c>
@@ -5241,12 +9249,12 @@
       <c r="P1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="Q1" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
       <c r="U1" s="6" t="s">
         <v>206</v>
       </c>
@@ -6718,744 +10726,914 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
       <c r="J34" s="25"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
       <c r="N34" s="21"/>
       <c r="O34" s="21"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="28"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="26"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="26"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
       <c r="J35" s="25"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
       <c r="N35" s="21"/>
       <c r="O35" s="21"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="25"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
       <c r="H36" s="22"/>
       <c r="I36" s="22"/>
       <c r="J36" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
       <c r="N36" s="21"/>
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="25"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
       <c r="H37" s="23"/>
       <c r="I37" s="23"/>
       <c r="J37" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
       <c r="N37" s="21"/>
       <c r="O37" s="21"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
       <c r="J38" s="25"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
       <c r="N38" s="21"/>
       <c r="O38" s="21"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
       <c r="J39" s="25"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
       <c r="N39" s="21"/>
       <c r="O39" s="21"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
       <c r="J40" s="25"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
       <c r="J41" s="25"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="21"/>
       <c r="O41" s="21"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="25"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
       <c r="J42" s="25"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
       <c r="N42" s="21"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="25"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
       <c r="J43" s="25"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
       <c r="N43" s="21"/>
       <c r="O43" s="21"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="25"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
       <c r="J44" s="25"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
       <c r="N44" s="21"/>
       <c r="O44" s="21"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="25"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
       <c r="J45" s="25"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
       <c r="N45" s="21"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="25"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
       <c r="J46" s="25"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
       <c r="N46" s="21"/>
       <c r="O46" s="21"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="25"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
       <c r="J47" s="25"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
       <c r="N47" s="21"/>
       <c r="O47" s="21"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="25"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
       <c r="J48" s="25"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
       <c r="N48" s="21"/>
       <c r="O48" s="21"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="25"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
       <c r="J49" s="25"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
       <c r="N49" s="21"/>
       <c r="O49" s="21"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
       <c r="J50" s="25"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
-      <c r="M50" s="28"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
       <c r="N50" s="21"/>
       <c r="O50" s="21"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="25"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
       <c r="J51" s="25"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26"/>
       <c r="N51" s="21"/>
       <c r="O51" s="21"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="25"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
       <c r="J52" s="25"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
       <c r="N52" s="21"/>
       <c r="O52" s="21"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="25"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
       <c r="J53" s="25"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
       <c r="N53" s="21"/>
       <c r="O53" s="21"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="25"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
       <c r="J54" s="25"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
       <c r="N54" s="21"/>
       <c r="O54" s="21"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="25"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
       <c r="J55" s="25"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
       <c r="N55" s="21"/>
       <c r="O55" s="21"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="25"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
       <c r="J56" s="25"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="28"/>
-      <c r="M56" s="28"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
       <c r="N56" s="21"/>
       <c r="O56" s="21"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="25"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
       <c r="J57" s="25"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
       <c r="N57" s="21"/>
       <c r="O57" s="21"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="25"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
       <c r="J58" s="25"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
       <c r="N58" s="21"/>
       <c r="O58" s="21"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="25"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
       <c r="J59" s="25"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="28"/>
-      <c r="M59" s="28"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
       <c r="N59" s="21"/>
       <c r="O59" s="21"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="25"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
       <c r="J60" s="25"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-      <c r="M60" s="28"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
       <c r="N60" s="21"/>
       <c r="O60" s="21"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="25"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
       <c r="J61" s="25"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
       <c r="N61" s="21"/>
       <c r="O61" s="21"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="25"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
       <c r="J62" s="25"/>
-      <c r="K62" s="28"/>
-      <c r="L62" s="28"/>
-      <c r="M62" s="28"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="26"/>
+      <c r="M62" s="26"/>
       <c r="N62" s="21"/>
       <c r="O62" s="21"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="25"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
       <c r="J63" s="25"/>
-      <c r="K63" s="28"/>
-      <c r="L63" s="28"/>
-      <c r="M63" s="28"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
       <c r="N63" s="21"/>
       <c r="O63" s="21"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="25"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
       <c r="J64" s="25"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
       <c r="N64" s="21"/>
       <c r="O64" s="21"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="25"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="28"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
       <c r="J65" s="25"/>
-      <c r="K65" s="28"/>
-      <c r="L65" s="28"/>
-      <c r="M65" s="28"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
       <c r="N65" s="21"/>
       <c r="O65" s="21"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="25"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
       <c r="J66" s="25"/>
-      <c r="K66" s="28"/>
-      <c r="L66" s="28"/>
-      <c r="M66" s="28"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="26"/>
+      <c r="M66" s="26"/>
       <c r="N66" s="21"/>
       <c r="O66" s="21"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="25"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
       <c r="J67" s="25"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
+      <c r="K67" s="26"/>
+      <c r="L67" s="26"/>
+      <c r="M67" s="26"/>
       <c r="N67" s="21"/>
       <c r="O67" s="21"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="25"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
       <c r="J68" s="25"/>
-      <c r="K68" s="28"/>
-      <c r="L68" s="28"/>
-      <c r="M68" s="28"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
       <c r="N68" s="21"/>
       <c r="O68" s="21"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="25"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
       <c r="J69" s="25"/>
-      <c r="K69" s="28"/>
-      <c r="L69" s="28"/>
-      <c r="M69" s="28"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="26"/>
       <c r="N69" s="21"/>
       <c r="O69" s="21"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="25"/>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
       <c r="J70" s="25"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
       <c r="N70" s="21"/>
       <c r="O70" s="21"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="25"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
       <c r="J71" s="25"/>
-      <c r="K71" s="28"/>
-      <c r="L71" s="28"/>
-      <c r="M71" s="28"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
       <c r="N71" s="21"/>
       <c r="O71" s="21"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="25"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
       <c r="J72" s="25"/>
-      <c r="K72" s="28"/>
-      <c r="L72" s="28"/>
-      <c r="M72" s="28"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
       <c r="N72" s="21"/>
       <c r="O72" s="21"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="25"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="28"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
       <c r="J73" s="25"/>
-      <c r="K73" s="28"/>
-      <c r="L73" s="28"/>
-      <c r="M73" s="28"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
       <c r="N73" s="21"/>
       <c r="O73" s="21"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="25"/>
-      <c r="B74" s="28"/>
-      <c r="C74" s="28"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
       <c r="J74" s="25"/>
-      <c r="K74" s="28"/>
-      <c r="L74" s="28"/>
-      <c r="M74" s="28"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
       <c r="N74" s="21"/>
       <c r="O74" s="21"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="25"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="28"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
       <c r="J75" s="25"/>
-      <c r="K75" s="28"/>
-      <c r="L75" s="28"/>
-      <c r="M75" s="28"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
       <c r="N75" s="21"/>
       <c r="O75" s="21"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="25"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
       <c r="J76" s="25"/>
-      <c r="K76" s="28"/>
-      <c r="L76" s="28"/>
-      <c r="M76" s="28"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
       <c r="N76" s="21"/>
       <c r="O76" s="21"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="25"/>
-      <c r="B77" s="28"/>
-      <c r="C77" s="28"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
       <c r="J77" s="25"/>
-      <c r="K77" s="28"/>
-      <c r="L77" s="28"/>
-      <c r="M77" s="28"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
       <c r="N77" s="21"/>
       <c r="O77" s="21"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="25"/>
-      <c r="B78" s="28"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
       <c r="J78" s="25"/>
-      <c r="K78" s="28"/>
-      <c r="L78" s="28"/>
-      <c r="M78" s="28"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
       <c r="N78" s="21"/>
       <c r="O78" s="21"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="25"/>
-      <c r="B79" s="28"/>
-      <c r="C79" s="28"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="28"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
       <c r="J79" s="25"/>
-      <c r="K79" s="28"/>
-      <c r="L79" s="28"/>
-      <c r="M79" s="28"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
       <c r="N79" s="21"/>
       <c r="O79" s="21"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="25"/>
-      <c r="B80" s="28"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="28"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
       <c r="J80" s="25"/>
-      <c r="K80" s="28"/>
-      <c r="L80" s="28"/>
-      <c r="M80" s="28"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
       <c r="N80" s="21"/>
       <c r="O80" s="21"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="25"/>
-      <c r="B81" s="28"/>
-      <c r="C81" s="28"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="28"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
       <c r="J81" s="25"/>
-      <c r="K81" s="28"/>
-      <c r="L81" s="28"/>
-      <c r="M81" s="28"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
       <c r="N81" s="21"/>
       <c r="O81" s="21"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="25"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="28"/>
-      <c r="D82" s="28"/>
-      <c r="E82" s="28"/>
-      <c r="F82" s="28"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
       <c r="J82" s="25"/>
-      <c r="K82" s="28"/>
-      <c r="L82" s="28"/>
-      <c r="M82" s="28"/>
+      <c r="K82" s="26"/>
+      <c r="L82" s="26"/>
+      <c r="M82" s="26"/>
       <c r="N82" s="21"/>
       <c r="O82" s="21"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="25"/>
-      <c r="B83" s="28"/>
-      <c r="C83" s="28"/>
-      <c r="D83" s="28"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="28"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
       <c r="J83" s="25"/>
-      <c r="K83" s="28"/>
-      <c r="L83" s="28"/>
-      <c r="M83" s="28"/>
+      <c r="K83" s="26"/>
+      <c r="L83" s="26"/>
+      <c r="M83" s="26"/>
       <c r="N83" s="21"/>
       <c r="O83" s="21"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="25"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
       <c r="J84" s="25"/>
-      <c r="K84" s="28"/>
-      <c r="L84" s="28"/>
-      <c r="M84" s="28"/>
+      <c r="K84" s="26"/>
+      <c r="L84" s="26"/>
+      <c r="M84" s="26"/>
       <c r="N84" s="21"/>
       <c r="O84" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="202">
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="J84:M84"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="J81:M81"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="J82:M82"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="Q10:T10"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="Q34:V34"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="J61:M61"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="J65:M65"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="J66:M66"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="J67:M67"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="J62:M62"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="J63:M63"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="J64:M64"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="J71:M71"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="J72:M72"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="J73:M73"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="J68:M68"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="J69:M69"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="J70:M70"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="J77:M77"/>
     <mergeCell ref="A78:F78"/>
@@ -7468,193 +11646,23 @@
     <mergeCell ref="J75:M75"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="J76:M76"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="J71:M71"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="J72:M72"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="J73:M73"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="J68:M68"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="J69:M69"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="J65:M65"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="J66:M66"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="J67:M67"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="J62:M62"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="J63:M63"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="J64:M64"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="J61:M61"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="Q33:T33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="Q34:V34"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="Q32:T32"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="Q29:T29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="Q30:T30"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="Q25:T25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="Q26:T26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="Q23:T23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="Q24:T24"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="Q22:T22"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="Q17:T17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="Q9:T9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="Q10:T10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="Q5:T5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="J84:M84"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="J81:M81"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="J82:M82"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
